--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -489,496 +489,499 @@
     <t>!bool</t>
   </si>
   <si>
+    <t>쌍검 기본공격</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Attack_Damage</t>
+  </si>
+  <si>
+    <t>쌍검 찌르기스킬</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Active_01_Damage</t>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+  </si>
+  <si>
+    <t>쌍검 강타스킬</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Active_02_Damage</t>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Passive_01</t>
+  </si>
+  <si>
+    <t>쌍검 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Attack</t>
+  </si>
+  <si>
+    <t>룬소드 기본공격</t>
+  </si>
+  <si>
+    <t>SE_RuneSword_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Active_01</t>
+  </si>
+  <si>
+    <t>룬소드 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Passive_01</t>
+  </si>
+  <si>
+    <t>룬소드 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Attack</t>
+  </si>
+  <si>
+    <t>석궁 기본공격</t>
+  </si>
+  <si>
+    <t>SE_CrossBow_Attack_Projectile</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Active_01</t>
+  </si>
+  <si>
+    <t>석궁 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Passive_01</t>
+  </si>
+  <si>
+    <t>석궁 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Attack</t>
+  </si>
+  <si>
+    <t>쌍권총 기본공격</t>
+  </si>
+  <si>
+    <t>SE_DualPistol_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Active_01</t>
+  </si>
+  <si>
+    <t>쌍권총 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Passive_01</t>
+  </si>
+  <si>
+    <t>쌍권총 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 근접 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_MeleeAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_RangeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 원거리 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Projectile</t>
+  </si>
+  <si>
+    <t>Skill_Monster_CastAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 캐스팅 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_CastAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_OrcGeneral_Active_01</t>
+  </si>
+  <si>
+    <t>오크장군 액티브스킬1</t>
+  </si>
+  <si>
+    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_Doom_01</t>
+  </si>
+  <si>
+    <t>보스 전멸기</t>
+  </si>
+  <si>
+    <t>SE_Boss_Doom_Damage</t>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectOrigin</t>
+  </si>
+  <si>
+    <t>EffectTime</t>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+  </si>
+  <si>
+    <t>EffectParam_3</t>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+  </si>
+  <si>
+    <t>EffectParam_5</t>
+  </si>
+  <si>
+    <t>ChainEffectIDs</t>
+  </si>
+  <si>
+    <t>OnHitTrigger</t>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+  </si>
+  <si>
+    <t>!SkillEffectOrigin</t>
+  </si>
+  <si>
+    <t>Stat_Atk</t>
+  </si>
+  <si>
+    <t>hit-blue</t>
+  </si>
+  <si>
+    <t>blade_hit_08</t>
+  </si>
+  <si>
+    <t>PJT_CrossBow_Bolt</t>
+  </si>
+  <si>
+    <t>SE_CrossBow_Attack_Damage</t>
+  </si>
+  <si>
+    <t>focus-hit-2</t>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+  </si>
+  <si>
+    <t>hit-orange</t>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>face_hit_finisher_40</t>
+  </si>
+  <si>
+    <t>PJT_Monster_Arrow</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Damage</t>
+  </si>
+  <si>
+    <t>fire-punch</t>
+  </si>
+  <si>
+    <t>fire_punch_finisher_06</t>
+  </si>
+  <si>
+    <t>SE_Common_Stagger_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_Stagger</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_BreakStun</t>
+  </si>
+  <si>
+    <t>SE_Monster_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_DamageTakenUp</t>
+  </si>
+  <si>
+    <t>SE_Debuff_DamageTakenUp_StatChange</t>
+  </si>
+  <si>
+    <t>StatDetail_DamageTakenAmp_Add</t>
+  </si>
+  <si>
+    <t>VFX_ImpactCritical_1.1.0_Pink</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_AtkUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Ratio</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_DefUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Ratio</t>
+  </si>
+  <si>
+    <t>SkillModifier</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Scope_Skill</t>
+  </si>
+  <si>
+    <t>Scope_Effect</t>
+  </si>
+  <si>
+    <t>Scope_Projectile</t>
+  </si>
+  <si>
+    <t>Scope_Summon</t>
+  </si>
+  <si>
+    <t>Scope_Buff</t>
+  </si>
+  <si>
+    <t>ParamKey</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>RefValue</t>
+  </si>
+  <si>
+    <t>!SkillModifier</t>
+  </si>
+  <si>
+    <t>!SkillModifierScope</t>
+  </si>
+  <si>
+    <t>!Projectile</t>
+  </si>
+  <si>
+    <t>!Summon</t>
+  </si>
+  <si>
+    <t>!Buff</t>
+  </si>
+  <si>
+    <t>!ModifierOperator</t>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>SkillParamDef</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!ParamDefValueTypes</t>
+  </si>
+  <si>
+    <t>비례 계수</t>
+  </si>
+  <si>
+    <t>FlatValue</t>
+  </si>
+  <si>
+    <t>고정 추가 데미지</t>
+  </si>
+  <si>
+    <t>HitCount</t>
+  </si>
+  <si>
+    <t>다단 타격 횟수</t>
+  </si>
+  <si>
+    <t>HitInterval</t>
+  </si>
+  <si>
+    <t>다단 타격 간격</t>
+  </si>
+  <si>
+    <t>ScaleStat</t>
+  </si>
+  <si>
+    <t>비례 기준 스탯</t>
+  </si>
+  <si>
+    <t>회복 비례 계수</t>
+  </si>
+  <si>
+    <t>고정 회복량</t>
+  </si>
+  <si>
+    <t>TickCount</t>
+  </si>
+  <si>
+    <t>지속 회복 횟수</t>
+  </si>
+  <si>
+    <t>TickInterval</t>
+  </si>
+  <si>
+    <t>회복 간격</t>
+  </si>
+  <si>
+    <t>RefID</t>
+  </si>
+  <si>
+    <t>부여할 버프</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>지속시간</t>
+  </si>
+  <si>
+    <t>StackMax</t>
+  </si>
+  <si>
+    <t>최대 중첩</t>
+  </si>
+  <si>
+    <t>효과 배율</t>
+  </si>
+  <si>
+    <t>Chance</t>
+  </si>
+  <si>
+    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
+  </si>
+  <si>
+    <t>변경할 스탯 + 연산 방식</t>
+  </si>
+  <si>
+    <t>수치</t>
+  </si>
+  <si>
+    <t>0 = 영구(패시브)</t>
+  </si>
+  <si>
+    <t>미사용</t>
+  </si>
+  <si>
+    <t>발사할 투사체</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>투사체 개수</t>
+  </si>
+  <si>
+    <t>Angle</t>
+  </si>
+  <si>
+    <t>투사체 간 분산각(도)</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>연속 발사 간격. 0=동시</t>
+  </si>
+  <si>
+    <t>SpeedRate</t>
+  </si>
+  <si>
+    <t>속도 배율</t>
+  </si>
+  <si>
+    <t>소환물</t>
+  </si>
+  <si>
+    <t>소환 개수</t>
+  </si>
+  <si>
+    <t>지속시간. 0=영구</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>배치/공전/장판 반경</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>TargetSkillID</t>
+  </si>
+  <si>
+    <t>쿨타임을 줄일 대상 스킬</t>
+  </si>
+  <si>
+    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
+  </si>
+  <si>
+    <t>고정 회복 시간(초)</t>
+  </si>
+  <si>
+    <t>소모할 버프</t>
+  </si>
+  <si>
+    <t>소모할 스택 수</t>
+  </si>
+  <si>
     <t>Skill_DualBlades_Attack</t>
-  </si>
-  <si>
-    <t>쌍검 기본공격</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>쌍검 찌르기스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualBlades_Active_02</t>
-  </si>
-  <si>
-    <t>쌍검 강타스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_02_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍검 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Attack</t>
-  </si>
-  <si>
-    <t>룬소드 기본공격</t>
-  </si>
-  <si>
-    <t>SE_RuneSword_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Active_01</t>
-  </si>
-  <si>
-    <t>룬소드 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Passive_01</t>
-  </si>
-  <si>
-    <t>룬소드 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Attack</t>
-  </si>
-  <si>
-    <t>석궁 기본공격</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Active_01</t>
-  </si>
-  <si>
-    <t>석궁 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Passive_01</t>
-  </si>
-  <si>
-    <t>석궁 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Attack</t>
-  </si>
-  <si>
-    <t>쌍권총 기본공격</t>
-  </si>
-  <si>
-    <t>SE_DualPistol_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Active_01</t>
-  </si>
-  <si>
-    <t>쌍권총 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍권총 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_Monster_MeleeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 근접 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_MeleeAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_RangeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 원거리 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_Monster_CastAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 캐스팅 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_CastAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_OrcGeneral_Active_01</t>
-  </si>
-  <si>
-    <t>오크장군 액티브스킬1</t>
-  </si>
-  <si>
-    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_Boss_Doom_01</t>
-  </si>
-  <si>
-    <t>보스 전멸기</t>
-  </si>
-  <si>
-    <t>SE_Boss_Doom_Damage</t>
-  </si>
-  <si>
-    <t>SkillEffect</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>EffectOrigin</t>
-  </si>
-  <si>
-    <t>EffectTime</t>
-  </si>
-  <si>
-    <t>EffectParam_1</t>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-  </si>
-  <si>
-    <t>EffectParam_3</t>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-  </si>
-  <si>
-    <t>EffectParam_5</t>
-  </si>
-  <si>
-    <t>ChainEffectIDs</t>
-  </si>
-  <si>
-    <t>OnHitTrigger</t>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-  </si>
-  <si>
-    <t>!SkillEffectOrigin</t>
-  </si>
-  <si>
-    <t>Stat_Atk</t>
-  </si>
-  <si>
-    <t>hit-blue</t>
-  </si>
-  <si>
-    <t>blade_hit_08</t>
-  </si>
-  <si>
-    <t>PJT_CrossBow_Bolt</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Damage</t>
-  </si>
-  <si>
-    <t>focus-hit-2</t>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-  </si>
-  <si>
-    <t>hit-orange</t>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>face_hit_finisher_40</t>
-  </si>
-  <si>
-    <t>PJT_Monster_Arrow</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Damage</t>
-  </si>
-  <si>
-    <t>fire-punch</t>
-  </si>
-  <si>
-    <t>fire_punch_finisher_06</t>
-  </si>
-  <si>
-    <t>SE_Common_Stagger_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_Stagger</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_BreakStun</t>
-  </si>
-  <si>
-    <t>SE_Monster_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_DamageTakenUp</t>
-  </si>
-  <si>
-    <t>SE_Debuff_DamageTakenUp_StatChange</t>
-  </si>
-  <si>
-    <t>StatDetail_DamageTakenAmp_Add</t>
-  </si>
-  <si>
-    <t>VFX_ImpactCritical_1.1.0_Pink</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_AtkUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Atk_Ratio</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_DefUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Def_Ratio</t>
-  </si>
-  <si>
-    <t>SkillModifier</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Scope_Skill</t>
-  </si>
-  <si>
-    <t>Scope_Effect</t>
-  </si>
-  <si>
-    <t>Scope_Projectile</t>
-  </si>
-  <si>
-    <t>Scope_Summon</t>
-  </si>
-  <si>
-    <t>Scope_Buff</t>
-  </si>
-  <si>
-    <t>ParamKey</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>RefValue</t>
-  </si>
-  <si>
-    <t>!SkillModifier</t>
-  </si>
-  <si>
-    <t>!SkillModifierScope</t>
-  </si>
-  <si>
-    <t>!Projectile</t>
-  </si>
-  <si>
-    <t>!Summon</t>
-  </si>
-  <si>
-    <t>!Buff</t>
-  </si>
-  <si>
-    <t>!ModifierOperator</t>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>SkillParamDef</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>ValueType</t>
-  </si>
-  <si>
-    <t>!int</t>
-  </si>
-  <si>
-    <t>!ParamDefValueTypes</t>
-  </si>
-  <si>
-    <t>비례 계수</t>
-  </si>
-  <si>
-    <t>FlatValue</t>
-  </si>
-  <si>
-    <t>고정 추가 데미지</t>
-  </si>
-  <si>
-    <t>HitCount</t>
-  </si>
-  <si>
-    <t>다단 타격 횟수</t>
-  </si>
-  <si>
-    <t>HitInterval</t>
-  </si>
-  <si>
-    <t>다단 타격 간격</t>
-  </si>
-  <si>
-    <t>ScaleStat</t>
-  </si>
-  <si>
-    <t>비례 기준 스탯</t>
-  </si>
-  <si>
-    <t>회복 비례 계수</t>
-  </si>
-  <si>
-    <t>고정 회복량</t>
-  </si>
-  <si>
-    <t>TickCount</t>
-  </si>
-  <si>
-    <t>지속 회복 횟수</t>
-  </si>
-  <si>
-    <t>TickInterval</t>
-  </si>
-  <si>
-    <t>회복 간격</t>
-  </si>
-  <si>
-    <t>RefID</t>
-  </si>
-  <si>
-    <t>부여할 버프</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>지속시간</t>
-  </si>
-  <si>
-    <t>StackMax</t>
-  </si>
-  <si>
-    <t>최대 중첩</t>
-  </si>
-  <si>
-    <t>효과 배율</t>
-  </si>
-  <si>
-    <t>Chance</t>
-  </si>
-  <si>
-    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
-  </si>
-  <si>
-    <t>변경할 스탯 + 연산 방식</t>
-  </si>
-  <si>
-    <t>수치</t>
-  </si>
-  <si>
-    <t>0 = 영구(패시브)</t>
-  </si>
-  <si>
-    <t>미사용</t>
-  </si>
-  <si>
-    <t>발사할 투사체</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>투사체 개수</t>
-  </si>
-  <si>
-    <t>Angle</t>
-  </si>
-  <si>
-    <t>투사체 간 분산각(도)</t>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>연속 발사 간격. 0=동시</t>
-  </si>
-  <si>
-    <t>SpeedRate</t>
-  </si>
-  <si>
-    <t>속도 배율</t>
-  </si>
-  <si>
-    <t>소환물</t>
-  </si>
-  <si>
-    <t>소환 개수</t>
-  </si>
-  <si>
-    <t>지속시간. 0=영구</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>배치/공전/장판 반경</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>TargetSkillID</t>
-  </si>
-  <si>
-    <t>쿨타임을 줄일 대상 스킬</t>
-  </si>
-  <si>
-    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
-  </si>
-  <si>
-    <t>고정 회복 시간(초)</t>
-  </si>
-  <si>
-    <t>소모할 버프</t>
-  </si>
-  <si>
-    <t>소모할 스택 수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1529,7 +1532,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2283,16 +2286,16 @@
     </row>
     <row r="4" spans="1:22">
       <c r="B4" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H4" s="6">
         <v>0.41670000000000001</v>
@@ -2316,7 +2319,7 @@
         <v>0.5</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V4">
         <v>1</v>
@@ -2324,10 +2327,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="B5" s="6" t="s">
-        <v>147</v>
+        <v>305</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>4</v>
@@ -2351,10 +2354,10 @@
         <v>0.5</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -2368,10 +2371,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="B6" s="6" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>4</v>
@@ -2395,7 +2398,7 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -2403,10 +2406,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>6</v>
@@ -2417,16 +2420,16 @@
     </row>
     <row r="8" spans="1:22">
       <c r="B8" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H8" s="6">
         <v>0.41670000000000001</v>
@@ -2450,7 +2453,7 @@
         <v>0.5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="V8">
         <v>1</v>
@@ -2458,10 +2461,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>4</v>
@@ -2472,10 +2475,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
@@ -2483,16 +2486,16 @@
     </row>
     <row r="11" spans="1:22">
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H11" s="6">
         <v>0.83333330000000005</v>
@@ -2516,7 +2519,7 @@
         <v>0.5</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="V11">
         <v>1</v>
@@ -2524,10 +2527,10 @@
     </row>
     <row r="12" spans="1:22">
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>4</v>
@@ -2538,10 +2541,10 @@
     </row>
     <row r="13" spans="1:22">
       <c r="B13" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>6</v>
@@ -2549,16 +2552,16 @@
     </row>
     <row r="14" spans="1:22">
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H14" s="6">
         <v>0.83333330000000005</v>
@@ -2582,7 +2585,7 @@
         <v>0.5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="V14">
         <v>1</v>
@@ -2590,10 +2593,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="B15" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>4</v>
@@ -2604,10 +2607,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="B16" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
@@ -2615,16 +2618,16 @@
     </row>
     <row r="17" spans="2:16">
       <c r="B17" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H17" s="6">
         <v>0.433</v>
@@ -2645,21 +2648,21 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H18" s="6">
         <v>0.83333330000000005</v>
@@ -2683,15 +2686,15 @@
         <v>0.5</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>2</v>
@@ -2724,15 +2727,15 @@
         <v>6</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>4</v>
@@ -2765,15 +2768,15 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
@@ -2803,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -2851,7 +2854,7 @@
         <v>112</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2872,40 +2875,40 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2913,10 +2916,10 @@
         <v>141</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>137</v>
@@ -2951,7 +2954,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>57</v>
@@ -2969,21 +2972,21 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
         <v>57</v>
@@ -3001,21 +3004,21 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>65</v>
@@ -3027,7 +3030,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3038,7 +3041,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
@@ -3053,21 +3056,21 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
         <v>57</v>
@@ -3085,21 +3088,21 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
         <v>57</v>
@@ -3117,15 +3120,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>65</v>
@@ -3137,7 +3140,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3148,7 +3151,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
         <v>57</v>
@@ -3163,15 +3166,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C12" t="s">
         <v>57</v>
@@ -3189,18 +3192,18 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
         <v>61</v>
@@ -3209,7 +3212,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G13">
         <v>0.4</v>
@@ -3217,7 +3220,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="B14" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
         <v>61</v>
@@ -3226,7 +3229,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -3234,7 +3237,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="B15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
         <v>61</v>
@@ -3243,7 +3246,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="B16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
         <v>61</v>
@@ -3260,7 +3263,7 @@
         <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -3268,7 +3271,7 @@
     </row>
     <row r="17" spans="2:15">
       <c r="B17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
         <v>63</v>
@@ -3277,7 +3280,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G17">
         <v>0.3</v>
@@ -3289,7 +3292,7 @@
     </row>
     <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
         <v>57</v>
@@ -3304,22 +3307,22 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K18" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
         <v>57</v>
@@ -3334,22 +3337,22 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>63</v>
@@ -3358,7 +3361,7 @@
         <v>53</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G20" s="6">
         <v>0.1</v>
@@ -3367,7 +3370,7 @@
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>63</v>
@@ -3376,7 +3379,7 @@
         <v>53</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G21" s="6">
         <v>0.1</v>
@@ -3385,7 +3388,7 @@
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
         <v>57</v>
@@ -3403,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
@@ -3411,7 +3414,7 @@
     </row>
     <row r="23" spans="2:15">
       <c r="B23" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C23" t="s">
         <v>57</v>
@@ -3429,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O23" s="4"/>
     </row>
@@ -3535,7 +3538,7 @@
         <v>112</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3555,42 +3558,42 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>134</v>
@@ -3599,19 +3602,19 @@
         <v>141</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>135</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>137</v>
@@ -3645,10 +3648,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3656,16 +3659,16 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>115</v>
@@ -3673,19 +3676,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>135</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>135</v>
@@ -3708,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3722,13 +3725,13 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F5" t="s">
         <v>97</v>
       </c>
       <c r="G5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3742,13 +3745,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F6" t="s">
         <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3762,13 +3765,13 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
         <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3782,13 +3785,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3808,7 +3811,7 @@
         <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3822,13 +3825,13 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F10" t="s">
         <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3842,13 +3845,13 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F11" t="s">
         <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3862,13 +3865,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F12" t="s">
         <v>97</v>
       </c>
       <c r="G12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3882,13 +3885,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3902,13 +3905,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F14" t="s">
         <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3922,13 +3925,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3942,13 +3945,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F16" t="s">
         <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -3968,7 +3971,7 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -3982,13 +3985,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F18" t="s">
         <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -4008,7 +4011,7 @@
         <v>106</v>
       </c>
       <c r="G19" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -4022,13 +4025,13 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
         <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -4042,13 +4045,13 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F21" t="s">
         <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -4062,7 +4065,7 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -4076,7 +4079,7 @@
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -4090,13 +4093,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F24" t="s">
         <v>102</v>
       </c>
       <c r="G24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -4110,13 +4113,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F25" t="s">
         <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -4130,13 +4133,13 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F26" t="s">
         <v>97</v>
       </c>
       <c r="G26" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -4150,13 +4153,13 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
         <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -4170,13 +4173,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F28" t="s">
         <v>97</v>
       </c>
       <c r="G28" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -4190,13 +4193,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F29" t="s">
         <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -4210,13 +4213,13 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F30" t="s">
         <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -4230,13 +4233,13 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F31" t="s">
         <v>97</v>
       </c>
       <c r="G31" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -4250,13 +4253,13 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F32" t="s">
         <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="2:7">
@@ -4270,7 +4273,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -4284,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F34" t="s">
         <v>97</v>
@@ -4301,7 +4304,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F35" t="s">
         <v>97</v>
@@ -4335,7 +4338,7 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="2:7">
@@ -4349,7 +4352,7 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="2:7">
@@ -4363,13 +4366,13 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F39" t="s">
         <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="2:7">
@@ -4389,7 +4392,7 @@
         <v>97</v>
       </c>
       <c r="G40" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="2:7">
@@ -4403,13 +4406,13 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F41" t="s">
         <v>97</v>
       </c>
       <c r="G41" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="2:7">
@@ -4423,7 +4426,7 @@
         <v>4</v>
       </c>
       <c r="G42" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="2:7">
@@ -4437,7 +4440,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="2:7">
@@ -4451,13 +4454,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F44" t="s">
         <v>104</v>
       </c>
       <c r="G44" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="2:7">
@@ -4471,13 +4474,13 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F45" t="s">
         <v>98</v>
       </c>
       <c r="G45" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -4491,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="2:7">
@@ -4505,7 +4508,7 @@
         <v>4</v>
       </c>
       <c r="G47" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="2:7">
@@ -4519,7 +4522,7 @@
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="2:2">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -501,505 +501,507 @@
     <t>SE_DualBlades_Attack_Damage</t>
   </si>
   <si>
+    <t>쌍검 찌르기스킬</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Active_01_Damage</t>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+  </si>
+  <si>
+    <t>쌍검 강타스킬</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Active_02_Damage</t>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Passive_01</t>
+  </si>
+  <si>
+    <t>쌍검 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Attack</t>
+  </si>
+  <si>
+    <t>룬소드 기본공격</t>
+  </si>
+  <si>
+    <t>SE_RuneSword_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Active_01</t>
+  </si>
+  <si>
+    <t>룬소드 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Passive_01</t>
+  </si>
+  <si>
+    <t>룬소드 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Attack</t>
+  </si>
+  <si>
+    <t>석궁 기본공격</t>
+  </si>
+  <si>
+    <t>SE_CrossBow_Attack_Projectile</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Active_01</t>
+  </si>
+  <si>
+    <t>석궁 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Passive_01</t>
+  </si>
+  <si>
+    <t>석궁 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Attack</t>
+  </si>
+  <si>
+    <t>쌍권총 기본공격</t>
+  </si>
+  <si>
+    <t>SE_DualPistol_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Active_01</t>
+  </si>
+  <si>
+    <t>쌍권총 강타스킬</t>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Passive_01</t>
+  </si>
+  <si>
+    <t>쌍권총 패시브 스킬</t>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 근접 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_MeleeAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_RangeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 원거리 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Projectile</t>
+  </si>
+  <si>
+    <t>Skill_Monster_CastAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 캐스팅 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_CastAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_OrcGeneral_Active_01</t>
+  </si>
+  <si>
+    <t>오크장군 액티브스킬1</t>
+  </si>
+  <si>
+    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_Doom_01</t>
+  </si>
+  <si>
+    <t>보스 전멸기</t>
+  </si>
+  <si>
+    <t>SE_Boss_Doom_Damage</t>
+  </si>
+  <si>
+    <t>Skill_SummonSpark_Attack</t>
+  </si>
+  <si>
+    <t>스파크 전기 빔</t>
+  </si>
+  <si>
+    <t>SE_SummonSpark_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Passive_02</t>
+  </si>
+  <si>
+    <t>쌍검 스파크 소환</t>
+  </si>
+  <si>
+    <t>SE_DualBlades_Passive_02_Summon</t>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectOrigin</t>
+  </si>
+  <si>
+    <t>EffectTime</t>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+  </si>
+  <si>
+    <t>EffectParam_3</t>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+  </si>
+  <si>
+    <t>EffectParam_5</t>
+  </si>
+  <si>
+    <t>ChainEffectIDs</t>
+  </si>
+  <si>
+    <t>OnHitTrigger</t>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+  </si>
+  <si>
+    <t>!SkillEffectOrigin</t>
+  </si>
+  <si>
+    <t>Stat_Atk</t>
+  </si>
+  <si>
+    <t>hit-blue</t>
+  </si>
+  <si>
+    <t>blade_hit_08</t>
+  </si>
+  <si>
+    <t>PJT_CrossBow_Bolt</t>
+  </si>
+  <si>
+    <t>SE_CrossBow_Attack_Damage</t>
+  </si>
+  <si>
+    <t>focus-hit-2</t>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+  </si>
+  <si>
+    <t>hit-orange</t>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>PJT_Monster_Arrow</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Damage</t>
+  </si>
+  <si>
+    <t>fire-punch</t>
+  </si>
+  <si>
+    <t>fire_punch_finisher_06</t>
+  </si>
+  <si>
+    <t>SE_Common_Stagger_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_Stagger</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_BreakStun</t>
+  </si>
+  <si>
+    <t>SE_Monster_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_DamageTakenUp</t>
+  </si>
+  <si>
+    <t>SE_Debuff_DamageTakenUp_StatChange</t>
+  </si>
+  <si>
+    <t>StatDetail_DamageTakenAmp_Add</t>
+  </si>
+  <si>
+    <t>VFX_ImpactCritical_1.1.0_Pink</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_AtkUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Ratio</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_DefUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Ratio</t>
+  </si>
+  <si>
+    <t>Summon_Spark</t>
+  </si>
+  <si>
+    <t>SkillModifier</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Scope_Skill</t>
+  </si>
+  <si>
+    <t>Scope_Effect</t>
+  </si>
+  <si>
+    <t>Scope_Projectile</t>
+  </si>
+  <si>
+    <t>Scope_Summon</t>
+  </si>
+  <si>
+    <t>Scope_Buff</t>
+  </si>
+  <si>
+    <t>ParamKey</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>RefValue</t>
+  </si>
+  <si>
+    <t>!SkillModifier</t>
+  </si>
+  <si>
+    <t>!SkillModifierScope</t>
+  </si>
+  <si>
+    <t>!Projectile</t>
+  </si>
+  <si>
+    <t>!Summon</t>
+  </si>
+  <si>
+    <t>!Buff</t>
+  </si>
+  <si>
+    <t>!ModifierOperator</t>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>SkillParamDef</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!ParamDefValueTypes</t>
+  </si>
+  <si>
+    <t>비례 계수</t>
+  </si>
+  <si>
+    <t>FlatValue</t>
+  </si>
+  <si>
+    <t>고정 추가 데미지</t>
+  </si>
+  <si>
+    <t>HitCount</t>
+  </si>
+  <si>
+    <t>다단 타격 횟수</t>
+  </si>
+  <si>
+    <t>HitInterval</t>
+  </si>
+  <si>
+    <t>다단 타격 간격</t>
+  </si>
+  <si>
+    <t>ScaleStat</t>
+  </si>
+  <si>
+    <t>비례 기준 스탯</t>
+  </si>
+  <si>
+    <t>회복 비례 계수</t>
+  </si>
+  <si>
+    <t>고정 회복량</t>
+  </si>
+  <si>
+    <t>TickCount</t>
+  </si>
+  <si>
+    <t>지속 회복 횟수</t>
+  </si>
+  <si>
+    <t>TickInterval</t>
+  </si>
+  <si>
+    <t>회복 간격</t>
+  </si>
+  <si>
+    <t>RefID</t>
+  </si>
+  <si>
+    <t>부여할 버프</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>지속시간</t>
+  </si>
+  <si>
+    <t>StackMax</t>
+  </si>
+  <si>
+    <t>최대 중첩</t>
+  </si>
+  <si>
+    <t>효과 배율</t>
+  </si>
+  <si>
+    <t>Chance</t>
+  </si>
+  <si>
+    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
+  </si>
+  <si>
+    <t>변경할 스탯 + 연산 방식</t>
+  </si>
+  <si>
+    <t>수치</t>
+  </si>
+  <si>
+    <t>0 = 영구(패시브)</t>
+  </si>
+  <si>
+    <t>미사용</t>
+  </si>
+  <si>
+    <t>발사할 투사체</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>투사체 개수</t>
+  </si>
+  <si>
+    <t>Angle</t>
+  </si>
+  <si>
+    <t>투사체 간 분산각(도)</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>연속 발사 간격. 0=동시</t>
+  </si>
+  <si>
+    <t>SpeedRate</t>
+  </si>
+  <si>
+    <t>속도 배율</t>
+  </si>
+  <si>
+    <t>소환물</t>
+  </si>
+  <si>
+    <t>소환 개수</t>
+  </si>
+  <si>
+    <t>지속시간. 0=영구</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>배치/공전/장판 반경</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>TargetSkillID</t>
+  </si>
+  <si>
+    <t>쿨타임을 줄일 대상 스킬</t>
+  </si>
+  <si>
+    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
+  </si>
+  <si>
+    <t>고정 회복 시간(초)</t>
+  </si>
+  <si>
+    <t>소모할 버프</t>
+  </si>
+  <si>
+    <t>소모할 스택 수</t>
+  </si>
+  <si>
+    <t>face_hit_small_23</t>
+  </si>
+  <si>
     <t>Skill_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>쌍검 찌르기스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualBlades_Active_02</t>
-  </si>
-  <si>
-    <t>쌍검 강타스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_02_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍검 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Attack</t>
-  </si>
-  <si>
-    <t>룬소드 기본공격</t>
-  </si>
-  <si>
-    <t>SE_RuneSword_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Active_01</t>
-  </si>
-  <si>
-    <t>룬소드 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Passive_01</t>
-  </si>
-  <si>
-    <t>룬소드 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Attack</t>
-  </si>
-  <si>
-    <t>석궁 기본공격</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Active_01</t>
-  </si>
-  <si>
-    <t>석궁 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Passive_01</t>
-  </si>
-  <si>
-    <t>석궁 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Attack</t>
-  </si>
-  <si>
-    <t>쌍권총 기본공격</t>
-  </si>
-  <si>
-    <t>SE_DualPistol_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Active_01</t>
-  </si>
-  <si>
-    <t>쌍권총 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍권총 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_Monster_MeleeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 근접 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_MeleeAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_RangeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 원거리 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_Monster_CastAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 캐스팅 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_CastAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_OrcGeneral_Active_01</t>
-  </si>
-  <si>
-    <t>오크장군 액티브스킬1</t>
-  </si>
-  <si>
-    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_Boss_Doom_01</t>
-  </si>
-  <si>
-    <t>보스 전멸기</t>
-  </si>
-  <si>
-    <t>SE_Boss_Doom_Damage</t>
-  </si>
-  <si>
-    <t>Skill_SummonSpark_Attack</t>
-  </si>
-  <si>
-    <t>스파크 전기 빔</t>
-  </si>
-  <si>
-    <t>SE_SummonSpark_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Passive_02</t>
-  </si>
-  <si>
-    <t>쌍검 스파크 소환</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Passive_02_Summon</t>
-  </si>
-  <si>
-    <t>SkillEffect</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>EffectOrigin</t>
-  </si>
-  <si>
-    <t>EffectTime</t>
-  </si>
-  <si>
-    <t>EffectParam_1</t>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-  </si>
-  <si>
-    <t>EffectParam_3</t>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-  </si>
-  <si>
-    <t>EffectParam_5</t>
-  </si>
-  <si>
-    <t>ChainEffectIDs</t>
-  </si>
-  <si>
-    <t>OnHitTrigger</t>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-  </si>
-  <si>
-    <t>!SkillEffectOrigin</t>
-  </si>
-  <si>
-    <t>Stat_Atk</t>
-  </si>
-  <si>
-    <t>hit-blue</t>
-  </si>
-  <si>
-    <t>blade_hit_08</t>
-  </si>
-  <si>
-    <t>PJT_CrossBow_Bolt</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Damage</t>
-  </si>
-  <si>
-    <t>focus-hit-2</t>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-  </si>
-  <si>
-    <t>hit-orange</t>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>PJT_Monster_Arrow</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Damage</t>
-  </si>
-  <si>
-    <t>fire-punch</t>
-  </si>
-  <si>
-    <t>fire_punch_finisher_06</t>
-  </si>
-  <si>
-    <t>SE_Common_Stagger_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_Stagger</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_BreakStun</t>
-  </si>
-  <si>
-    <t>SE_Monster_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_DamageTakenUp</t>
-  </si>
-  <si>
-    <t>SE_Debuff_DamageTakenUp_StatChange</t>
-  </si>
-  <si>
-    <t>StatDetail_DamageTakenAmp_Add</t>
-  </si>
-  <si>
-    <t>VFX_ImpactCritical_1.1.0_Pink</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_AtkUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Atk_Ratio</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_DefUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Def_Ratio</t>
-  </si>
-  <si>
-    <t>Summon_Spark</t>
-  </si>
-  <si>
-    <t>SkillModifier</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Scope_Skill</t>
-  </si>
-  <si>
-    <t>Scope_Effect</t>
-  </si>
-  <si>
-    <t>Scope_Projectile</t>
-  </si>
-  <si>
-    <t>Scope_Summon</t>
-  </si>
-  <si>
-    <t>Scope_Buff</t>
-  </si>
-  <si>
-    <t>ParamKey</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>RefValue</t>
-  </si>
-  <si>
-    <t>!SkillModifier</t>
-  </si>
-  <si>
-    <t>!SkillModifierScope</t>
-  </si>
-  <si>
-    <t>!Projectile</t>
-  </si>
-  <si>
-    <t>!Summon</t>
-  </si>
-  <si>
-    <t>!Buff</t>
-  </si>
-  <si>
-    <t>!ModifierOperator</t>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>SkillParamDef</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>ValueType</t>
-  </si>
-  <si>
-    <t>!int</t>
-  </si>
-  <si>
-    <t>!ParamDefValueTypes</t>
-  </si>
-  <si>
-    <t>비례 계수</t>
-  </si>
-  <si>
-    <t>FlatValue</t>
-  </si>
-  <si>
-    <t>고정 추가 데미지</t>
-  </si>
-  <si>
-    <t>HitCount</t>
-  </si>
-  <si>
-    <t>다단 타격 횟수</t>
-  </si>
-  <si>
-    <t>HitInterval</t>
-  </si>
-  <si>
-    <t>다단 타격 간격</t>
-  </si>
-  <si>
-    <t>ScaleStat</t>
-  </si>
-  <si>
-    <t>비례 기준 스탯</t>
-  </si>
-  <si>
-    <t>회복 비례 계수</t>
-  </si>
-  <si>
-    <t>고정 회복량</t>
-  </si>
-  <si>
-    <t>TickCount</t>
-  </si>
-  <si>
-    <t>지속 회복 횟수</t>
-  </si>
-  <si>
-    <t>TickInterval</t>
-  </si>
-  <si>
-    <t>회복 간격</t>
-  </si>
-  <si>
-    <t>RefID</t>
-  </si>
-  <si>
-    <t>부여할 버프</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>지속시간</t>
-  </si>
-  <si>
-    <t>StackMax</t>
-  </si>
-  <si>
-    <t>최대 중첩</t>
-  </si>
-  <si>
-    <t>효과 배율</t>
-  </si>
-  <si>
-    <t>Chance</t>
-  </si>
-  <si>
-    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
-  </si>
-  <si>
-    <t>변경할 스탯 + 연산 방식</t>
-  </si>
-  <si>
-    <t>수치</t>
-  </si>
-  <si>
-    <t>0 = 영구(패시브)</t>
-  </si>
-  <si>
-    <t>미사용</t>
-  </si>
-  <si>
-    <t>발사할 투사체</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>투사체 개수</t>
-  </si>
-  <si>
-    <t>Angle</t>
-  </si>
-  <si>
-    <t>투사체 간 분산각(도)</t>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>연속 발사 간격. 0=동시</t>
-  </si>
-  <si>
-    <t>SpeedRate</t>
-  </si>
-  <si>
-    <t>속도 배율</t>
-  </si>
-  <si>
-    <t>소환물</t>
-  </si>
-  <si>
-    <t>소환 개수</t>
-  </si>
-  <si>
-    <t>지속시간. 0=영구</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>배치/공전/장판 반경</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>TargetSkillID</t>
-  </si>
-  <si>
-    <t>쿨타임을 줄일 대상 스킬</t>
-  </si>
-  <si>
-    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
-  </si>
-  <si>
-    <t>고정 회복 시간(초)</t>
-  </si>
-  <si>
-    <t>소모할 버프</t>
-  </si>
-  <si>
-    <t>소모할 스택 수</t>
-  </si>
-  <si>
-    <t>face_hit_small_23</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1550,7 +1552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2345,10 +2347,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="B5" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>4</v>
@@ -2372,10 +2374,10 @@
         <v>0.5</v>
       </c>
       <c r="P5" t="s">
+        <v>148</v>
+      </c>
+      <c r="R5" t="s">
         <v>149</v>
-      </c>
-      <c r="R5" t="s">
-        <v>150</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -2389,10 +2391,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="B6" s="6" t="s">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>4</v>
@@ -2416,7 +2418,7 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -2424,10 +2426,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>6</v>
@@ -2438,10 +2440,10 @@
     </row>
     <row r="8" spans="1:22">
       <c r="B8" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
@@ -2471,7 +2473,7 @@
         <v>0.5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="V8">
         <v>1</v>
@@ -2479,10 +2481,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>4</v>
@@ -2493,10 +2495,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
@@ -2504,10 +2506,10 @@
     </row>
     <row r="11" spans="1:22">
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
@@ -2537,7 +2539,7 @@
         <v>0.5</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V11">
         <v>1</v>
@@ -2545,10 +2547,10 @@
     </row>
     <row r="12" spans="1:22">
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>4</v>
@@ -2559,10 +2561,10 @@
     </row>
     <row r="13" spans="1:22">
       <c r="B13" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>6</v>
@@ -2570,10 +2572,10 @@
     </row>
     <row r="14" spans="1:22">
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
@@ -2603,7 +2605,7 @@
         <v>0.5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="V14">
         <v>1</v>
@@ -2611,10 +2613,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="B15" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>4</v>
@@ -2625,10 +2627,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="B16" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
@@ -2636,10 +2638,10 @@
     </row>
     <row r="17" spans="2:16">
       <c r="B17" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>2</v>
@@ -2666,15 +2668,15 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
@@ -2704,15 +2706,15 @@
         <v>0.5</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>2</v>
@@ -2745,15 +2747,15 @@
         <v>6</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>4</v>
@@ -2786,15 +2788,15 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
@@ -2824,15 +2826,15 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F22" t="s">
         <v>2</v>
@@ -2856,15 +2858,15 @@
         <v>0.25</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -2876,7 +2878,7 @@
         <v>35</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -2921,7 +2923,7 @@
         <v>112</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2942,40 +2944,40 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2983,10 +2985,10 @@
         <v>141</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>137</v>
@@ -3039,21 +3041,21 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
         <v>57</v>
@@ -3071,21 +3073,21 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>65</v>
@@ -3097,7 +3099,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3108,7 +3110,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
@@ -3123,21 +3125,21 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
         <v>57</v>
@@ -3155,21 +3157,21 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
         <v>57</v>
@@ -3187,15 +3189,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>65</v>
@@ -3207,7 +3209,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3218,7 +3220,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
         <v>57</v>
@@ -3233,15 +3235,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N11" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
         <v>57</v>
@@ -3259,18 +3261,18 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
         <v>61</v>
@@ -3279,7 +3281,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G13">
         <v>0.4</v>
@@ -3287,7 +3289,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="B14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
         <v>61</v>
@@ -3296,7 +3298,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -3304,7 +3306,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="B15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
         <v>61</v>
@@ -3313,7 +3315,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3321,7 +3323,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="B16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
         <v>61</v>
@@ -3330,7 +3332,7 @@
         <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -3338,7 +3340,7 @@
     </row>
     <row r="17" spans="2:15">
       <c r="B17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C17" t="s">
         <v>63</v>
@@ -3347,7 +3349,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G17">
         <v>0.3</v>
@@ -3359,7 +3361,7 @@
     </row>
     <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
         <v>57</v>
@@ -3374,22 +3376,22 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
+        <v>211</v>
+      </c>
+      <c r="K18" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18" t="s">
+        <v>212</v>
+      </c>
+      <c r="N18" t="s">
         <v>213</v>
-      </c>
-      <c r="K18" t="s">
-        <v>226</v>
-      </c>
-      <c r="M18" t="s">
-        <v>214</v>
-      </c>
-      <c r="N18" t="s">
-        <v>215</v>
       </c>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
         <v>57</v>
@@ -3404,22 +3406,22 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>63</v>
@@ -3428,7 +3430,7 @@
         <v>53</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G20" s="6">
         <v>0.1</v>
@@ -3437,7 +3439,7 @@
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>63</v>
@@ -3446,7 +3448,7 @@
         <v>53</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G21" s="6">
         <v>0.1</v>
@@ -3455,7 +3457,7 @@
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s">
         <v>57</v>
@@ -3473,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
@@ -3481,7 +3483,7 @@
     </row>
     <row r="23" spans="2:15">
       <c r="B23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C23" t="s">
         <v>57</v>
@@ -3499,13 +3501,13 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="2:15">
       <c r="B24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
@@ -3523,7 +3525,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -3532,7 +3534,7 @@
     </row>
     <row r="25" spans="2:15">
       <c r="B25" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
         <v>67</v>
@@ -3544,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -3654,7 +3656,7 @@
         <v>112</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3674,42 +3676,42 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>134</v>
@@ -3718,19 +3720,19 @@
         <v>141</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>135</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>137</v>
@@ -3764,10 +3766,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3775,16 +3777,16 @@
         <v>113</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>115</v>
@@ -3792,19 +3794,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>135</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>135</v>
@@ -3827,7 +3829,7 @@
         <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3841,13 +3843,13 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F5" t="s">
         <v>97</v>
       </c>
       <c r="G5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3861,13 +3863,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F6" t="s">
         <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3881,13 +3883,13 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F7" t="s">
         <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3901,13 +3903,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3927,7 +3929,7 @@
         <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3941,13 +3943,13 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
         <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3961,13 +3963,13 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F11" t="s">
         <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3981,13 +3983,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
         <v>97</v>
       </c>
       <c r="G12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4001,13 +4003,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4021,13 +4023,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F14" t="s">
         <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4041,13 +4043,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F15" t="s">
         <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4061,13 +4063,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F16" t="s">
         <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -4087,7 +4089,7 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -4101,13 +4103,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F18" t="s">
         <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -4127,7 +4129,7 @@
         <v>106</v>
       </c>
       <c r="G19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -4141,13 +4143,13 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F20" t="s">
         <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -4161,13 +4163,13 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F21" t="s">
         <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -4181,7 +4183,7 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -4195,7 +4197,7 @@
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -4209,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F24" t="s">
         <v>102</v>
       </c>
       <c r="G24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -4229,13 +4231,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F25" t="s">
         <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -4249,13 +4251,13 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F26" t="s">
         <v>97</v>
       </c>
       <c r="G26" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -4269,13 +4271,13 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F27" t="s">
         <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -4289,13 +4291,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F28" t="s">
         <v>97</v>
       </c>
       <c r="G28" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -4309,13 +4311,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F29" t="s">
         <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -4329,13 +4331,13 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
         <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -4349,13 +4351,13 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F31" t="s">
         <v>97</v>
       </c>
       <c r="G31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -4369,13 +4371,13 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F32" t="s">
         <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="2:7">
@@ -4389,7 +4391,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -4403,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F34" t="s">
         <v>97</v>
@@ -4420,7 +4422,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F35" t="s">
         <v>97</v>
@@ -4454,7 +4456,7 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="2:7">
@@ -4468,7 +4470,7 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="2:7">
@@ -4482,13 +4484,13 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F39" t="s">
         <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="2:7">
@@ -4508,7 +4510,7 @@
         <v>97</v>
       </c>
       <c r="G40" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="2:7">
@@ -4522,13 +4524,13 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F41" t="s">
         <v>97</v>
       </c>
       <c r="G41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="2:7">
@@ -4542,7 +4544,7 @@
         <v>4</v>
       </c>
       <c r="G42" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="2:7">
@@ -4556,7 +4558,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="2:7">
@@ -4570,13 +4572,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F44" t="s">
         <v>104</v>
       </c>
       <c r="G44" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="2:7">
@@ -4590,13 +4592,13 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F45" t="s">
         <v>98</v>
       </c>
       <c r="G45" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -4610,7 +4612,7 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="2:7">
@@ -4624,7 +4626,7 @@
         <v>4</v>
       </c>
       <c r="G47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="2:7">
@@ -4638,7 +4640,7 @@
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="2:2">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="383">
   <si>
     <t>!Enum</t>
   </si>
@@ -84,1033 +84,1206 @@
     <t>패시브</t>
   </si>
   <si>
+    <t>CastingTypes에 의해 CastingParam이 결정된다.</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>즉시발동</t>
+  </si>
+  <si>
+    <t>Casting</t>
+  </si>
+  <si>
+    <t>시전 시간 경과 후 발동</t>
+  </si>
+  <si>
+    <t>시간시간</t>
+  </si>
+  <si>
+    <t>발동 확률</t>
+  </si>
+  <si>
+    <t>OnCombo</t>
+  </si>
+  <si>
+    <t>n번째 타격마다 발동</t>
+  </si>
+  <si>
+    <t>공격 횟수</t>
+  </si>
+  <si>
+    <t>OnCrit</t>
+  </si>
+  <si>
+    <t>크리티컬시 확률 발동</t>
+  </si>
+  <si>
+    <t>OnDamaged</t>
+  </si>
+  <si>
+    <t>피격 시 확률 발동</t>
+  </si>
+  <si>
+    <t>OnLowHP</t>
+  </si>
+  <si>
+    <t>체력이 일정 % 이하일때 발동</t>
+  </si>
+  <si>
+    <t>체력 퍼센트</t>
+  </si>
+  <si>
+    <t>OnKill</t>
+  </si>
+  <si>
+    <t>적 사망시 확률로 발동</t>
+  </si>
+  <si>
+    <t>Aura</t>
+  </si>
+  <si>
+    <t>시전자 주변 지속 발동</t>
+  </si>
+  <si>
+    <t>발동 주기</t>
+  </si>
+  <si>
+    <t>상시 적용</t>
+  </si>
+  <si>
+    <t>SkillApplyTarget</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>시전자 자신</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>적 진영</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>아군 진영</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>모두</t>
+  </si>
+  <si>
+    <t>SkillScanTypes</t>
+  </si>
+  <si>
+    <t>SkillScanTypes에 의해 ScanParam이 결정된다.</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>원형</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>부채꼴</t>
+  </si>
+  <si>
+    <t>각도</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>직선 궤적</t>
+  </si>
+  <si>
+    <t>넓이</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>지정대상</t>
+  </si>
+  <si>
+    <t>타겟수</t>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>데미지</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>회복</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>버프/디버프 부여(기절,침묵,슬로우 등)</t>
+  </si>
+  <si>
+    <t>StatChange</t>
+  </si>
+  <si>
+    <t>스탯 변경 (패시브·오라용)</t>
+  </si>
+  <si>
+    <t>Projectile</t>
+  </si>
+  <si>
+    <t>투사체 발사</t>
+  </si>
+  <si>
+    <t>Summon</t>
+  </si>
+  <si>
+    <t>소환물 생성</t>
+  </si>
+  <si>
+    <t>Force</t>
+  </si>
+  <si>
+    <t>밀기, 당기기, 위치이동</t>
+  </si>
+  <si>
+    <t>CooldownReduce</t>
+  </si>
+  <si>
+    <t>쿨다운감소</t>
+  </si>
+  <si>
+    <t>BuffConsume</t>
+  </si>
+  <si>
+    <t>버프 스택 소모</t>
+  </si>
+  <si>
+    <t>SkillEffectOrigin</t>
+  </si>
+  <si>
+    <t>Caster</t>
+  </si>
+  <si>
+    <t>스킬을 직접 사용한 주체</t>
+  </si>
+  <si>
+    <t>스킬의 주 효과를 받는 대상</t>
+  </si>
+  <si>
+    <t>Attacker</t>
+  </si>
+  <si>
+    <t>나에게 피해를 입힌 주체</t>
+  </si>
+  <si>
+    <t>Victim</t>
+  </si>
+  <si>
+    <t>내가 피해를 입힌 대상</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>소환물의 주인</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>위치기반</t>
+  </si>
+  <si>
+    <t>SkillModifierScope</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>ModifierOperator</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>Append</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>ParamDefValueTypes</t>
+  </si>
+  <si>
+    <t>Float</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>Bool</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>EffectID</t>
+  </si>
+  <si>
+    <t>ProjectileID</t>
+  </si>
+  <si>
+    <t>SummonID</t>
+  </si>
+  <si>
+    <t>BuffID</t>
+  </si>
+  <si>
+    <t>StatID</t>
+  </si>
+  <si>
+    <t>StatDetailID</t>
+  </si>
+  <si>
+    <t>ForceType</t>
+  </si>
+  <si>
+    <t>Push</t>
+  </si>
+  <si>
+    <t>밀어냄</t>
+  </si>
+  <si>
+    <t>Pull</t>
+  </si>
+  <si>
+    <t>당김</t>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+  </si>
+  <si>
+    <t>!ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>SkillCategory</t>
+  </si>
+  <si>
+    <t>AnimName</t>
+  </si>
+  <si>
+    <t>AnimLength</t>
+  </si>
+  <si>
+    <t>CastingType</t>
+  </si>
+  <si>
+    <t>CastingParam</t>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+  </si>
+  <si>
+    <t>ScanType</t>
+  </si>
+  <si>
+    <t>ScanRange</t>
+  </si>
+  <si>
+    <t>ScanParam</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>EffectID_01</t>
+  </si>
+  <si>
+    <t>EffectID_02</t>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+  </si>
+  <si>
+    <t>SkillVFXFacing</t>
+  </si>
+  <si>
+    <t>SkillVFXOffset</t>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+  </si>
+  <si>
+    <t>!Skill</t>
+  </si>
+  <si>
+    <t>!string</t>
+  </si>
+  <si>
+    <t>!SkillCategoryTypes</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>!SkillCastingTypes</t>
+  </si>
+  <si>
+    <t>!SkillApplyTarget</t>
+  </si>
+  <si>
+    <t>!SkillScanTypes</t>
+  </si>
+  <si>
+    <t>!SkillEffect</t>
+  </si>
+  <si>
+    <t>!bool</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 근접 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_MeleeAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_RangeAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 원거리 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Projectile</t>
+  </si>
+  <si>
+    <t>Skill_Monster_CastAttack_01</t>
+  </si>
+  <si>
+    <t>몬스터 캐스팅 공격</t>
+  </si>
+  <si>
+    <t>SE_Monster_CastAttack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_OrcGeneral_Active_01</t>
+  </si>
+  <si>
+    <t>오크장군 액티브스킬1</t>
+  </si>
+  <si>
+    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_Doom_01</t>
+  </si>
+  <si>
+    <t>보스 전멸기</t>
+  </si>
+  <si>
+    <t>SE_Boss_Doom_Damage</t>
+  </si>
+  <si>
+    <t>Skill_SummonSpark_Attack</t>
+  </si>
+  <si>
+    <t>스파크 전기 빔</t>
+  </si>
+  <si>
+    <t>SE_SummonSpark_Attack_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Rift_Burst</t>
+  </si>
+  <si>
+    <t>균열 폭발</t>
+  </si>
+  <si>
+    <t>주변의 모든 적에게 공격력의 300% 피해를 준다.</t>
+  </si>
+  <si>
+    <t>skill_001</t>
+  </si>
+  <si>
+    <t>SE_Rift_Burst_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Rift_Bind</t>
+  </si>
+  <si>
+    <t>균열 속박</t>
+  </si>
+  <si>
+    <t>주변의 모든 적에게 공격력의 100% 피해를 주고 3초간 기절시킨다.</t>
+  </si>
+  <si>
+    <t>skill_002</t>
+  </si>
+  <si>
+    <t>SE_Rift_Bind_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Rift_Storm</t>
+  </si>
+  <si>
+    <t>균열 폭풍</t>
+  </si>
+  <si>
+    <t>주변의 모든 적에게 공격력의 80% 피해를 5회 연속으로 준다.</t>
+  </si>
+  <si>
+    <t>skill_003</t>
+  </si>
+  <si>
+    <t>SE_Rift_Storm_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Rift_Spirit</t>
+  </si>
+  <si>
+    <t>균열 정령</t>
+  </si>
+  <si>
+    <t>15초 동안 적을 공격하는 정령 3마리를 소환한다.</t>
+  </si>
+  <si>
+    <t>skill_004</t>
+  </si>
+  <si>
+    <t>SE_Rift_Spirit_Summon</t>
+  </si>
+  <si>
+    <t>Skill_Rift_Collapse</t>
+  </si>
+  <si>
+    <t>균열 붕괴</t>
+  </si>
+  <si>
+    <t>넓은 범위의 모든 적에게 공격력의 600% 피해를 주고 받는 피해를 증가시킨다.</t>
+  </si>
+  <si>
+    <t>skill_005</t>
+  </si>
+  <si>
+    <t>SE_Rift_Collapse_Damage</t>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectOrigin</t>
+  </si>
+  <si>
+    <t>EffectTime</t>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+  </si>
+  <si>
+    <t>EffectParam_3</t>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+  </si>
+  <si>
+    <t>EffectParam_5</t>
+  </si>
+  <si>
+    <t>ChainEffectIDs</t>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+  </si>
+  <si>
+    <t>!SkillEffectOrigin</t>
+  </si>
+  <si>
+    <t>Stat_Atk</t>
+  </si>
+  <si>
+    <t>hit-blue</t>
+  </si>
+  <si>
+    <t>blade_hit_08</t>
+  </si>
+  <si>
+    <t>focus-hit-2</t>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+  </si>
+  <si>
+    <t>hit-orange</t>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>face_hit_small_23</t>
+  </si>
+  <si>
+    <t>PJT_Monster_Arrow</t>
+  </si>
+  <si>
+    <t>SE_Monster_RangeAttack_Damage</t>
+  </si>
+  <si>
+    <t>fire-punch</t>
+  </si>
+  <si>
+    <t>fire_punch_finisher_06</t>
+  </si>
+  <si>
+    <t>SE_Common_Stagger_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_Stagger</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_BreakStun</t>
+  </si>
+  <si>
+    <t>SE_Monster_Break_Stun_Buff</t>
+  </si>
+  <si>
+    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
+  </si>
+  <si>
+    <t>BUFF_DamageTakenUp</t>
+  </si>
+  <si>
+    <t>SE_Debuff_DamageTakenUp_StatChange</t>
+  </si>
+  <si>
+    <t>StatDetail_DamageTakenAmp_Add</t>
+  </si>
+  <si>
+    <t>VFX_ImpactCritical_1.1.0_Pink</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_AtkUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Ratio</t>
+  </si>
+  <si>
+    <t>SE_BuffRune_DefUp</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Ratio</t>
+  </si>
+  <si>
+    <t>Summon_Spark</t>
+  </si>
+  <si>
+    <t>StatDetail_AtkSpeed_Add</t>
+  </si>
+  <si>
+    <t>SE_Rift_Bind_Stun</t>
+  </si>
+  <si>
+    <t>BUFF_Stun</t>
+  </si>
+  <si>
+    <t>SkillModifier</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Scope_Skill</t>
+  </si>
+  <si>
+    <t>Scope_Effect</t>
+  </si>
+  <si>
+    <t>Scope_Projectile</t>
+  </si>
+  <si>
+    <t>Scope_Summon</t>
+  </si>
+  <si>
+    <t>Scope_Buff</t>
+  </si>
+  <si>
+    <t>ParamKey</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>RefValue</t>
+  </si>
+  <si>
+    <t>!SkillModifier</t>
+  </si>
+  <si>
+    <t>!SkillModifierScope</t>
+  </si>
+  <si>
+    <t>!Projectile</t>
+  </si>
+  <si>
+    <t>!Summon</t>
+  </si>
+  <si>
+    <t>!Buff</t>
+  </si>
+  <si>
+    <t>!ModifierOperator</t>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>SkillParamDef</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
+    <t>!ParamDefValueTypes</t>
+  </si>
+  <si>
+    <t>비례 계수</t>
+  </si>
+  <si>
+    <t>FlatValue</t>
+  </si>
+  <si>
+    <t>고정 추가 데미지</t>
+  </si>
+  <si>
+    <t>HitCount</t>
+  </si>
+  <si>
+    <t>다단 타격 횟수</t>
+  </si>
+  <si>
+    <t>HitInterval</t>
+  </si>
+  <si>
+    <t>다단 타격 간격</t>
+  </si>
+  <si>
+    <t>ScaleStat</t>
+  </si>
+  <si>
+    <t>비례 기준 스탯</t>
+  </si>
+  <si>
+    <t>회복 비례 계수</t>
+  </si>
+  <si>
+    <t>고정 회복량</t>
+  </si>
+  <si>
+    <t>TickCount</t>
+  </si>
+  <si>
+    <t>지속 회복 횟수</t>
+  </si>
+  <si>
+    <t>TickInterval</t>
+  </si>
+  <si>
+    <t>회복 간격</t>
+  </si>
+  <si>
+    <t>RefID</t>
+  </si>
+  <si>
+    <t>부여할 버프</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>지속시간</t>
+  </si>
+  <si>
+    <t>StackMax</t>
+  </si>
+  <si>
+    <t>최대 중첩</t>
+  </si>
+  <si>
+    <t>효과 배율</t>
+  </si>
+  <si>
+    <t>Chance</t>
+  </si>
+  <si>
+    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
+  </si>
+  <si>
+    <t>변경할 스탯 + 연산 방식</t>
+  </si>
+  <si>
+    <t>수치</t>
+  </si>
+  <si>
+    <t>0 = 영구(패시브)</t>
+  </si>
+  <si>
+    <t>미사용</t>
+  </si>
+  <si>
+    <t>발사할 투사체</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>투사체 개수</t>
+  </si>
+  <si>
+    <t>Angle</t>
+  </si>
+  <si>
+    <t>투사체 간 분산각(도)</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>연속 발사 간격. 0=동시</t>
+  </si>
+  <si>
+    <t>SpeedRate</t>
+  </si>
+  <si>
+    <t>속도 배율</t>
+  </si>
+  <si>
+    <t>소환물</t>
+  </si>
+  <si>
+    <t>소환 개수</t>
+  </si>
+  <si>
+    <t>지속시간. 0=영구</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>배치/공전/장판 반경</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>TargetSkillID</t>
+  </si>
+  <si>
+    <t>쿨타임을 줄일 대상 스킬</t>
+  </si>
+  <si>
+    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
+  </si>
+  <si>
+    <t>고정 회복 시간(초)</t>
+  </si>
+  <si>
+    <t>소모할 버프</t>
+  </si>
+  <si>
+    <t>소모할 스택 수</t>
+  </si>
+  <si>
+    <t>SE_Ruins_Hazard_Damage</t>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_MeleeAttack_01</t>
+  </si>
+  <si>
+    <t>보스 근접 공격</t>
+  </si>
+  <si>
+    <t>OnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>SkillCastingTypes</t>
-  </si>
-  <si>
-    <t>CastingTypes에 의해 CastingParam이 결정된다.</t>
-  </si>
-  <si>
-    <t>Instant</t>
-  </si>
-  <si>
-    <t>즉시발동</t>
-  </si>
-  <si>
-    <t>Casting</t>
-  </si>
-  <si>
-    <t>시전 시간 경과 후 발동</t>
-  </si>
-  <si>
-    <t>시간시간</t>
-  </si>
-  <si>
-    <t>OnHit</t>
-  </si>
-  <si>
-    <t>공격 적중 시 확률 발동</t>
-  </si>
-  <si>
-    <t>발동 확률</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSwingHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>OnCombo</t>
-  </si>
-  <si>
-    <t>n번째 타격마다 발동</t>
-  </si>
-  <si>
-    <t>공격 횟수</t>
-  </si>
-  <si>
-    <t>OnCrit</t>
-  </si>
-  <si>
-    <t>크리티컬시 확률 발동</t>
-  </si>
-  <si>
-    <t>OnDamaged</t>
-  </si>
-  <si>
-    <t>피격 시 확률 발동</t>
-  </si>
-  <si>
-    <t>OnLowHP</t>
-  </si>
-  <si>
-    <t>체력이 일정 % 이하일때 발동</t>
-  </si>
-  <si>
-    <t>체력 퍼센트</t>
-  </si>
-  <si>
-    <t>OnKill</t>
-  </si>
-  <si>
-    <t>적 사망시 확률로 발동</t>
-  </si>
-  <si>
-    <t>Aura</t>
-  </si>
-  <si>
-    <t>시전자 주변 지속 발동</t>
-  </si>
-  <si>
-    <t>발동 주기</t>
-  </si>
-  <si>
-    <t>상시 적용</t>
-  </si>
-  <si>
-    <t>SkillApplyTarget</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>시전자 자신</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>적 진영</t>
-  </si>
-  <si>
-    <t>Friendly</t>
-  </si>
-  <si>
-    <t>아군 진영</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>모두</t>
-  </si>
-  <si>
-    <t>SkillScanTypes</t>
-  </si>
-  <si>
-    <t>SkillScanTypes에 의해 ScanParam이 결정된다.</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>원형</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>부채꼴</t>
-  </si>
-  <si>
-    <t>각도</t>
-  </si>
-  <si>
-    <t>Line</t>
-  </si>
-  <si>
-    <t>직선 궤적</t>
-  </si>
-  <si>
-    <t>넓이</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>지정대상</t>
-  </si>
-  <si>
-    <t>타겟수</t>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>데미지</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>회복</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>버프/디버프 부여(기절,침묵,슬로우 등)</t>
-  </si>
-  <si>
-    <t>StatChange</t>
-  </si>
-  <si>
-    <t>스탯 변경 (패시브·오라용)</t>
-  </si>
-  <si>
-    <t>Projectile</t>
-  </si>
-  <si>
-    <t>투사체 발사</t>
-  </si>
-  <si>
-    <t>Summon</t>
-  </si>
-  <si>
-    <t>소환물 생성</t>
-  </si>
-  <si>
-    <t>Force</t>
-  </si>
-  <si>
-    <t>밀기, 당기기, 위치이동</t>
-  </si>
-  <si>
-    <t>CooldownReduce</t>
-  </si>
-  <si>
-    <t>쿨다운감소</t>
-  </si>
-  <si>
-    <t>BuffConsume</t>
-  </si>
-  <si>
-    <t>버프 스택 소모</t>
-  </si>
-  <si>
-    <t>SkillEffectOrigin</t>
-  </si>
-  <si>
-    <t>Caster</t>
-  </si>
-  <si>
-    <t>스킬을 직접 사용한 주체</t>
-  </si>
-  <si>
-    <t>스킬의 주 효과를 받는 대상</t>
-  </si>
-  <si>
-    <t>Attacker</t>
-  </si>
-  <si>
-    <t>나에게 피해를 입힌 주체</t>
-  </si>
-  <si>
-    <t>Victim</t>
-  </si>
-  <si>
-    <t>내가 피해를 입힌 대상</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>소환물의 주인</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>위치기반</t>
-  </si>
-  <si>
-    <t>SkillModifierScope</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>Effect</t>
-  </si>
-  <si>
-    <t>ModifierOperator</t>
-  </si>
-  <si>
-    <t>Replace</t>
-  </si>
-  <si>
-    <t>Append</t>
-  </si>
-  <si>
-    <t>Set</t>
-  </si>
-  <si>
-    <t>Add</t>
-  </si>
-  <si>
-    <t>Ratio</t>
-  </si>
-  <si>
-    <t>ParamDefValueTypes</t>
-  </si>
-  <si>
-    <t>Float</t>
-  </si>
-  <si>
-    <t>Int</t>
-  </si>
-  <si>
-    <t>Bool</t>
-  </si>
-  <si>
-    <t>SkillID</t>
-  </si>
-  <si>
-    <t>EffectID</t>
-  </si>
-  <si>
-    <t>ProjectileID</t>
-  </si>
-  <si>
-    <t>SummonID</t>
-  </si>
-  <si>
-    <t>BuffID</t>
-  </si>
-  <si>
-    <t>StatID</t>
-  </si>
-  <si>
-    <t>StatDetailID</t>
-  </si>
-  <si>
-    <t>ForceType</t>
-  </si>
-  <si>
-    <t>Push</t>
-  </si>
-  <si>
-    <t>밀어냄</t>
-  </si>
-  <si>
-    <t>Pull</t>
-  </si>
-  <si>
-    <t>당김</t>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-  </si>
-  <si>
-    <t>!ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>SkillCategory</t>
-  </si>
-  <si>
-    <t>AnimName</t>
-  </si>
-  <si>
-    <t>AnimLength</t>
-  </si>
-  <si>
-    <t>CastingType</t>
-  </si>
-  <si>
-    <t>CastingParam</t>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-  </si>
-  <si>
-    <t>ScanType</t>
-  </si>
-  <si>
-    <t>ScanRange</t>
-  </si>
-  <si>
-    <t>ScanParam</t>
-  </si>
-  <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
-    <t>EffectID_01</t>
-  </si>
-  <si>
-    <t>EffectID_02</t>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-  </si>
-  <si>
-    <t>SkillVFXFacing</t>
-  </si>
-  <si>
-    <t>SkillVFXOffset</t>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-  </si>
-  <si>
-    <t>BreakDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 적중 시 피격자별 확률 발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 적중 시 한번 확률 발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 찌르기스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Active_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_02_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Blade_Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도 기본공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Blade_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Blade_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Blade_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Pistol_Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총 기본공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Pistol_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Pistol_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Pistol_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rifle_Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총 기본공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Rifle_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rifle_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rifle_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Passive_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 스파크 소환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Passive_02_Summon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Blade_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Pistol_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJT_Pistol_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Pistol_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Rifle_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_02_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Passive_02_Summon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_AtkSpeedUp_StatChange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_AtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_GreatSword_AtkSpeedUp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_Active_01_Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_Active_01_AppendAtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_AtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_AtkSpeedBuff_Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_02_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_03_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboNext</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!Skill</t>
-  </si>
-  <si>
-    <t>!string</t>
-  </si>
-  <si>
-    <t>!SkillCategoryTypes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_02</t>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_02_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_03</t>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_03_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 기본공격 2타</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 기본공격 3타</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-  </si>
-  <si>
-    <t>!SkillCastingTypes</t>
-  </si>
-  <si>
-    <t>!SkillApplyTarget</t>
-  </si>
-  <si>
-    <t>!SkillScanTypes</t>
-  </si>
-  <si>
-    <t>!SkillEffect</t>
-  </si>
-  <si>
-    <t>!bool</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Attack</t>
-  </si>
-  <si>
-    <t>쌍검 기본공격</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>쌍검 찌르기스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Active_02</t>
-  </si>
-  <si>
-    <t>쌍검 강타스킬</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_02_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍검 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Attack</t>
-  </si>
-  <si>
-    <t>룬소드 기본공격</t>
-  </si>
-  <si>
-    <t>SE_RuneSword_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Active_01</t>
-  </si>
-  <si>
-    <t>룬소드 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Passive_01</t>
-  </si>
-  <si>
-    <t>룬소드 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Attack</t>
-  </si>
-  <si>
-    <t>석궁 기본공격</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Active_01</t>
-  </si>
-  <si>
-    <t>석궁 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Passive_01</t>
-  </si>
-  <si>
-    <t>석궁 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Attack</t>
-  </si>
-  <si>
-    <t>쌍권총 기본공격</t>
-  </si>
-  <si>
-    <t>SE_DualPistol_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Active_01</t>
-  </si>
-  <si>
-    <t>쌍권총 강타스킬</t>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Passive_01</t>
-  </si>
-  <si>
-    <t>쌍권총 패시브 스킬</t>
-  </si>
-  <si>
-    <t>Skill_Monster_MeleeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 근접 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_MeleeAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_RangeAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 원거리 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Projectile</t>
-  </si>
-  <si>
-    <t>Skill_Monster_CastAttack_01</t>
-  </si>
-  <si>
-    <t>몬스터 캐스팅 공격</t>
-  </si>
-  <si>
-    <t>SE_Monster_CastAttack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_OrcGeneral_Active_01</t>
-  </si>
-  <si>
-    <t>오크장군 액티브스킬1</t>
-  </si>
-  <si>
-    <t>SE_Monster_OrcGeneral_Active_01_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_Boss_Doom_01</t>
-  </si>
-  <si>
-    <t>보스 전멸기</t>
-  </si>
-  <si>
-    <t>SE_Boss_Doom_Damage</t>
-  </si>
-  <si>
-    <t>Skill_SummonSpark_Attack</t>
-  </si>
-  <si>
-    <t>스파크 전기 빔</t>
-  </si>
-  <si>
-    <t>SE_SummonSpark_Attack_Damage</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Passive_02</t>
-  </si>
-  <si>
-    <t>쌍검 스파크 소환</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Passive_02_Summon</t>
-  </si>
-  <si>
-    <t>Skill_Rift_Burst</t>
-  </si>
-  <si>
-    <t>균열 폭발</t>
-  </si>
-  <si>
-    <t>주변의 모든 적에게 공격력의 300% 피해를 준다.</t>
-  </si>
-  <si>
-    <t>skill_001</t>
-  </si>
-  <si>
-    <t>SE_Rift_Burst_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Rift_Bind</t>
-  </si>
-  <si>
-    <t>균열 속박</t>
-  </si>
-  <si>
-    <t>주변의 모든 적에게 공격력의 100% 피해를 주고 3초간 기절시킨다.</t>
-  </si>
-  <si>
-    <t>skill_002</t>
-  </si>
-  <si>
-    <t>SE_Rift_Bind_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Rift_Storm</t>
-  </si>
-  <si>
-    <t>균열 폭풍</t>
-  </si>
-  <si>
-    <t>주변의 모든 적에게 공격력의 80% 피해를 5회 연속으로 준다.</t>
-  </si>
-  <si>
-    <t>skill_003</t>
-  </si>
-  <si>
-    <t>SE_Rift_Storm_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Rift_Spirit</t>
-  </si>
-  <si>
-    <t>균열 정령</t>
-  </si>
-  <si>
-    <t>15초 동안 적을 공격하는 정령 3마리를 소환한다.</t>
-  </si>
-  <si>
-    <t>skill_004</t>
-  </si>
-  <si>
-    <t>SE_Rift_Spirit_Summon</t>
-  </si>
-  <si>
-    <t>Skill_Rift_Collapse</t>
-  </si>
-  <si>
-    <t>균열 붕괴</t>
-  </si>
-  <si>
-    <t>넓은 범위의 모든 적에게 공격력의 600% 피해를 주고 받는 피해를 증가시킨다.</t>
-  </si>
-  <si>
-    <t>skill_005</t>
-  </si>
-  <si>
-    <t>SE_Rift_Collapse_Damage</t>
-  </si>
-  <si>
-    <t>SkillEffect</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>EffectOrigin</t>
-  </si>
-  <si>
-    <t>EffectTime</t>
-  </si>
-  <si>
-    <t>EffectParam_1</t>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-  </si>
-  <si>
-    <t>EffectParam_3</t>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-  </si>
-  <si>
-    <t>EffectParam_5</t>
-  </si>
-  <si>
-    <t>ChainEffectIDs</t>
-  </si>
-  <si>
-    <t>OnHitTrigger</t>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-  </si>
-  <si>
-    <t>!SkillEffectOrigin</t>
-  </si>
-  <si>
-    <t>Stat_Atk</t>
-  </si>
-  <si>
-    <t>hit-blue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboClose</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboOpen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 기본공격 1타</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>blade_hit_08</t>
-  </si>
-  <si>
-    <t>PJT_CrossBow_Bolt</t>
-  </si>
-  <si>
-    <t>SE_CrossBow_Attack_Damage</t>
-  </si>
-  <si>
-    <t>focus-hit-2</t>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-  </si>
-  <si>
-    <t>hit-orange</t>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>face_hit_small_23</t>
-  </si>
-  <si>
-    <t>PJT_Monster_Arrow</t>
-  </si>
-  <si>
-    <t>SE_Monster_RangeAttack_Damage</t>
-  </si>
-  <si>
-    <t>fire-punch</t>
-  </si>
-  <si>
-    <t>fire_punch_finisher_06</t>
-  </si>
-  <si>
-    <t>SE_Common_Stagger_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_Stagger</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_BreakStun</t>
-  </si>
-  <si>
-    <t>SE_Monster_Break_Stun_Buff</t>
-  </si>
-  <si>
-    <t>SE_Boss_Break_DamageTakenUp_Buff</t>
-  </si>
-  <si>
-    <t>BUFF_DamageTakenUp</t>
-  </si>
-  <si>
-    <t>SE_Debuff_DamageTakenUp_StatChange</t>
-  </si>
-  <si>
-    <t>StatDetail_DamageTakenAmp_Add</t>
-  </si>
-  <si>
-    <t>VFX_ImpactCritical_1.1.0_Pink</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_AtkUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Atk_Ratio</t>
-  </si>
-  <si>
-    <t>SE_BuffRune_DefUp</t>
-  </si>
-  <si>
-    <t>StatDetail_Def_Ratio</t>
-  </si>
-  <si>
-    <t>Summon_Spark</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_AtkSpeedUp_StatChange</t>
-  </si>
-  <si>
-    <t>StatDetail_AtkSpeed_Add</t>
-  </si>
-  <si>
-    <t>SE_DualBlades_Active_01_AtkSpeedBuff</t>
-  </si>
-  <si>
-    <t>BUFF_DualBlades_AtkSpeedUp</t>
-  </si>
-  <si>
-    <t>SE_Rift_Bind_Stun</t>
-  </si>
-  <si>
-    <t>BUFF_Stun</t>
-  </si>
-  <si>
-    <t>SkillModifier</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Scope_Skill</t>
-  </si>
-  <si>
-    <t>Scope_Effect</t>
-  </si>
-  <si>
-    <t>Scope_Projectile</t>
-  </si>
-  <si>
-    <t>Scope_Summon</t>
-  </si>
-  <si>
-    <t>Scope_Buff</t>
-  </si>
-  <si>
-    <t>ParamKey</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>RefValue</t>
-  </si>
-  <si>
-    <t>!SkillModifier</t>
-  </si>
-  <si>
-    <t>!SkillModifierScope</t>
-  </si>
-  <si>
-    <t>!Projectile</t>
-  </si>
-  <si>
-    <t>!Summon</t>
-  </si>
-  <si>
-    <t>!Buff</t>
-  </si>
-  <si>
-    <t>!ModifierOperator</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_Active_01_Ratio</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_Active_01_AppendAtkSpeedBuff</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_AtkSpeedBuff_Ratio</t>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>SkillParamDef</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>ValueType</t>
-  </si>
-  <si>
-    <t>!int</t>
-  </si>
-  <si>
-    <t>!ParamDefValueTypes</t>
-  </si>
-  <si>
-    <t>비례 계수</t>
-  </si>
-  <si>
-    <t>FlatValue</t>
-  </si>
-  <si>
-    <t>고정 추가 데미지</t>
-  </si>
-  <si>
-    <t>HitCount</t>
-  </si>
-  <si>
-    <t>다단 타격 횟수</t>
-  </si>
-  <si>
-    <t>HitInterval</t>
-  </si>
-  <si>
-    <t>다단 타격 간격</t>
-  </si>
-  <si>
-    <t>ScaleStat</t>
-  </si>
-  <si>
-    <t>비례 기준 스탯</t>
-  </si>
-  <si>
-    <t>회복 비례 계수</t>
-  </si>
-  <si>
-    <t>고정 회복량</t>
-  </si>
-  <si>
-    <t>TickCount</t>
-  </si>
-  <si>
-    <t>지속 회복 횟수</t>
-  </si>
-  <si>
-    <t>TickInterval</t>
-  </si>
-  <si>
-    <t>회복 간격</t>
-  </si>
-  <si>
-    <t>RefID</t>
-  </si>
-  <si>
-    <t>부여할 버프</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>지속시간</t>
-  </si>
-  <si>
-    <t>StackMax</t>
-  </si>
-  <si>
-    <t>최대 중첩</t>
-  </si>
-  <si>
-    <t>효과 배율</t>
-  </si>
-  <si>
-    <t>Chance</t>
-  </si>
-  <si>
-    <t>부여 확률. 기절/둔화의 적용 확률도 여기</t>
-  </si>
-  <si>
-    <t>변경할 스탯 + 연산 방식</t>
-  </si>
-  <si>
-    <t>수치</t>
-  </si>
-  <si>
-    <t>0 = 영구(패시브)</t>
-  </si>
-  <si>
-    <t>미사용</t>
-  </si>
-  <si>
-    <t>발사할 투사체</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>투사체 개수</t>
-  </si>
-  <si>
-    <t>Angle</t>
-  </si>
-  <si>
-    <t>투사체 간 분산각(도)</t>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>연속 발사 간격. 0=동시</t>
-  </si>
-  <si>
-    <t>SpeedRate</t>
-  </si>
-  <si>
-    <t>속도 배율</t>
-  </si>
-  <si>
-    <t>소환물</t>
-  </si>
-  <si>
-    <t>소환 개수</t>
-  </si>
-  <si>
-    <t>지속시간. 0=영구</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>배치/공전/장판 반경</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>TargetSkillID</t>
-  </si>
-  <si>
-    <t>쿨타임을 줄일 대상 스킬</t>
-  </si>
-  <si>
-    <t>최대 쿨타임 대비 회복 비율. 1.0 = 초기화</t>
-  </si>
-  <si>
-    <t>고정 회복 시간(초)</t>
-  </si>
-  <si>
-    <t>소모할 버프</t>
-  </si>
-  <si>
-    <t>소모할 스택 수</t>
-  </si>
-  <si>
-    <t>SE_Ruins_Hazard_Damage</t>
-  </si>
-  <si>
-    <t>Skill_Monster_Boss_MeleeAttack_01</t>
-  </si>
-  <si>
-    <t>보스 근접 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1661,7 +1834,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1669,14 +1842,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="36.75" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2.5" style="18" customWidth="1"/>
-    <col min="5" max="5" width="150.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="16" width="9" style="4" customWidth="1"/>
     <col min="17" max="16384" width="9" style="4"/>
   </cols>
@@ -1721,61 +1894,61 @@
         <v>0</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="17"/>
       <c r="E6" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="6" t="s">
-        <v>15</v>
+        <v>305</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>17</v>
@@ -1783,463 +1956,474 @@
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="5" customFormat="1">
-      <c r="A18" s="7" t="s">
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1">
+      <c r="A19" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="20"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>36</v>
-      </c>
+      <c r="B19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="B22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="5" customFormat="1">
+      <c r="A25" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="5" customFormat="1">
-      <c r="A24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="9"/>
-      <c r="B25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="9"/>
       <c r="B26" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="9"/>
       <c r="B27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="19"/>
+        <v>44</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="E27" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="9"/>
       <c r="B28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="9"/>
+      <c r="B29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="5" customFormat="1">
+      <c r="A31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="5" customFormat="1">
-      <c r="A30" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>58</v>
-      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="21"/>
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="B33" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="B35" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="B36" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="B37" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="B38" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="B39" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="5" customFormat="1">
-      <c r="A41" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="B40" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="5" customFormat="1">
+      <c r="A42" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="20"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="B42" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="B42" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="20"/>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="6" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="B44" s="6" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="B45" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="B47" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="5" customFormat="1">
-      <c r="A49" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="5" customFormat="1">
+      <c r="A50" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="20"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="B50" s="6" t="s">
-        <v>88</v>
-      </c>
+      <c r="B50" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="20"/>
     </row>
     <row r="51" spans="1:5">
       <c r="B51" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="B52" s="6" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="B53" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" s="5" customFormat="1">
-      <c r="A56" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="B55" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="5" customFormat="1">
+      <c r="A57" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="20"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" s="6" t="s">
-        <v>91</v>
-      </c>
+      <c r="B57" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="20"/>
     </row>
     <row r="58" spans="1:5">
       <c r="B58" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="B59" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="B60" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="B61" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" s="5" customFormat="1">
-      <c r="A63" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="B62" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="5" customFormat="1">
+      <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="20"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="B64" s="6" t="s">
-        <v>97</v>
-      </c>
+      <c r="B64" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="20"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="20"/>
     </row>
     <row r="65" spans="1:5">
       <c r="B65" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="B66" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="B67" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="B68" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="B69" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="B70" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="B71" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="B72" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="B73" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" s="5" customFormat="1">
-      <c r="A76" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" s="5" customFormat="1">
+      <c r="A77" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" s="20"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="20"/>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="B77" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>109</v>
-      </c>
+      <c r="B77" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="20"/>
     </row>
     <row r="78" spans="1:5">
       <c r="B78" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="B79" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2251,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="13" customWidth="1"/>
@@ -2271,210 +2455,240 @@
     <col min="20" max="20" width="13.75" style="6" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.25" style="6" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="29" width="9" style="6" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="6"/>
+    <col min="23" max="23" width="30.625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="12.625" style="6" customWidth="1"/>
+    <col min="25" max="25" width="14.625" style="6" customWidth="1"/>
+    <col min="26" max="30" width="9" style="6" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="10" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:25" s="10" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="B2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="B2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="S2" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="T2" t="s">
         <v>128</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>130</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
+        <v>362</v>
+      </c>
+      <c r="X2" t="s">
+        <v>376</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="B3" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="V2" t="s">
+      <c r="D3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="B3" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="J3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="M3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="S3" t="s">
         <v>139</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="S3" t="s">
-        <v>142</v>
-      </c>
       <c r="T3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="V3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>134</v>
+      </c>
+      <c r="W3" t="s">
+        <v>363</v>
+      </c>
+      <c r="X3" t="s">
+        <v>374</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="B4" s="6" t="s">
-        <v>143</v>
+        <v>377</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>144</v>
+        <v>378</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>145</v>
+        <v>379</v>
       </c>
       <c r="H4" s="6">
-        <v>0.41670000000000001</v>
+        <v>1</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="6">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="O4" s="6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>146</v>
+        <v>380</v>
       </c>
       <c r="V4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="W4" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="X4" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="B5" s="6" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>148</v>
+        <v>312</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J5" s="6">
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -2483,10 +2697,10 @@
         <v>0.5</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="R5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -2498,27 +2712,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:25">
       <c r="B6" s="6" t="s">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>152</v>
+        <v>315</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>4</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6" s="6">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <v>1.5</v>
@@ -2527,50 +2741,50 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>316</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:25">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>317</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>318</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="B8" s="6" t="s">
-        <v>156</v>
+        <v>319</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>320</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H8" s="6">
         <v>0.41670000000000001</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M8" s="6">
         <v>1.2</v>
@@ -2582,18 +2796,18 @@
         <v>0.5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>158</v>
+        <v>321</v>
       </c>
       <c r="V8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:25">
       <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>322</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>4</v>
@@ -2602,41 +2816,41 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:25">
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>162</v>
+        <v>325</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:25">
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H11" s="6">
         <v>0.83333330000000005</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M11" s="6">
         <v>2.5</v>
@@ -2648,18 +2862,18 @@
         <v>0.5</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
       <c r="V11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:25">
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>4</v>
@@ -2668,41 +2882,41 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:25">
       <c r="B13" s="6" t="s">
-        <v>168</v>
+        <v>331</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>169</v>
+        <v>332</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:25">
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>171</v>
+        <v>334</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H14" s="6">
         <v>0.83333330000000005</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M14" s="6">
         <v>2</v>
@@ -2714,18 +2928,18 @@
         <v>0.5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>172</v>
+        <v>335</v>
       </c>
       <c r="V14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:25">
       <c r="B15" s="6" t="s">
-        <v>173</v>
+        <v>336</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
+        <v>337</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>4</v>
@@ -2734,41 +2948,41 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:25">
       <c r="B16" s="6" t="s">
-        <v>175</v>
+        <v>338</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
+        <v>339</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:22">
+    <row r="17" spans="2:25">
       <c r="B17" s="6" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H17" s="6">
         <v>0.433</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M17" s="6">
         <v>0.5</v>
@@ -2777,33 +2991,33 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="2:22">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25">
       <c r="B18" s="6" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H18" s="6">
         <v>0.83333330000000005</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M18" s="6">
         <v>2</v>
@@ -2815,36 +3029,36 @@
         <v>0.5</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25">
       <c r="B19" s="6" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H19" s="6">
         <v>0.76700000000000002</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" s="6">
         <v>1.5</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M19" s="6">
         <v>2.5</v>
@@ -2856,36 +3070,36 @@
         <v>6</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25">
       <c r="B20" s="6" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H20" s="6">
         <v>0.6</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J20" s="6">
         <v>1</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M20" s="6">
         <v>2</v>
@@ -2897,36 +3111,36 @@
         <v>5</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="2:22">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25">
       <c r="B21" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="F21" t="s">
         <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H21">
         <v>0.76700000000000002</v>
       </c>
       <c r="I21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J21">
         <v>8</v>
       </c>
       <c r="K21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2935,27 +3149,27 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25">
       <c r="B22" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="F22" t="s">
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M22">
         <v>3</v>
@@ -2967,15 +3181,15 @@
         <v>0.25</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25">
       <c r="B23" s="4" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>341</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -2984,202 +3198,202 @@
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25">
       <c r="B24" s="4" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
         <v>4</v>
       </c>
       <c r="I24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:22">
+    <row r="25" spans="2:25">
       <c r="B25" s="4" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="E25" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="F25" t="s">
         <v>4</v>
       </c>
       <c r="I25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M25">
         <v>5</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="V25">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:22">
+    <row r="26" spans="2:25">
       <c r="B26" s="4" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s">
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:22">
+    <row r="27" spans="2:25">
       <c r="B27" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="E27" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="F27" t="s">
         <v>4</v>
       </c>
       <c r="I27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:22">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25">
       <c r="B28" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="F28" t="s">
         <v>4</v>
       </c>
       <c r="I28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M28">
         <v>10</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="2:22">
+    <row r="29" spans="2:25">
       <c r="B29" s="6" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H29" s="6">
         <v>0.433</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M29" s="6">
         <v>1.2</v>
@@ -3188,7 +3402,104 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25">
+      <c r="B30" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" s="6">
+        <v>2</v>
+      </c>
+      <c r="N30" s="6">
+        <v>240</v>
+      </c>
+      <c r="O30" s="6">
+        <v>1</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="X30" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25">
+      <c r="B31" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="H31" s="6">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31" s="6">
+        <v>2</v>
+      </c>
+      <c r="N31" s="6">
+        <v>240</v>
+      </c>
+      <c r="O31" s="6">
+        <v>1</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="X31" s="6">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>
@@ -3221,10 +3532,10 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3242,127 +3553,127 @@
     </row>
     <row r="2" spans="1:15">
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="B3" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="6" t="s">
-        <v>146</v>
+        <v>381</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="F4" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>240</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>343</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E5" s="6">
         <v>0.6</v>
@@ -3374,33 +3685,33 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>165</v>
+        <v>344</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
+        <v>345</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3411,13 +3722,13 @@
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>242</v>
+        <v>346</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>1.1000000000000001</v>
@@ -3426,27 +3737,27 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="N7" t="s">
-        <v>244</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -3458,27 +3769,27 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>0.8</v>
@@ -3490,27 +3801,27 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3521,13 +3832,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>1.1000000000000001</v>
@@ -3536,21 +3847,21 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="N11" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E12" s="6">
         <v>0.8</v>
@@ -3562,27 +3873,27 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="G13">
         <v>0.4</v>
@@ -3590,16 +3901,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="B14" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -3607,16 +3918,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="B15" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3624,16 +3935,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="B16" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -3641,16 +3952,16 @@
     </row>
     <row r="17" spans="2:15">
       <c r="B17" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="G17">
         <v>0.3</v>
@@ -3662,13 +3973,13 @@
     </row>
     <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>149</v>
+        <v>348</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>2.5</v>
@@ -3677,28 +3988,28 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="K18" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>153</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F19">
         <v>2.5</v>
@@ -3707,31 +4018,31 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="K19" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="6" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="G20" s="6">
         <v>0.1</v>
@@ -3740,16 +4051,16 @@
     </row>
     <row r="21" spans="2:15">
       <c r="B21" s="6" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="G21" s="6">
         <v>0.1</v>
@@ -3758,13 +4069,13 @@
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="6" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E22">
         <v>0.7</v>
@@ -3776,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
@@ -3784,13 +4095,13 @@
     </row>
     <row r="23" spans="2:15">
       <c r="B23" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E23">
         <v>0.6</v>
@@ -3802,19 +4113,19 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="2:15">
       <c r="B24" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3826,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -3835,19 +4146,19 @@
     </row>
     <row r="25" spans="2:15">
       <c r="B25" t="s">
-        <v>197</v>
+        <v>350</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -3862,16 +4173,16 @@
     </row>
     <row r="26" spans="2:15">
       <c r="B26" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3880,16 +4191,16 @@
     </row>
     <row r="27" spans="2:15">
       <c r="B27" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -3901,13 +4212,13 @@
     </row>
     <row r="28" spans="2:15">
       <c r="B28" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -3916,28 +4227,28 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="M28" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="N28" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="2:15">
       <c r="B29" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="G29">
         <v>3</v>
@@ -3946,13 +4257,13 @@
     </row>
     <row r="30" spans="2:15">
       <c r="B30" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -3961,28 +4272,28 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="K30" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="M30" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="N30" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="2:15">
       <c r="B31" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F31">
         <v>0.8</v>
@@ -3994,28 +4305,28 @@
         <v>0.3</v>
       </c>
       <c r="J31" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="M31" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="N31" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="2:15">
       <c r="B32" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -4032,13 +4343,13 @@
     </row>
     <row r="33" spans="2:15">
       <c r="B33" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F33">
         <v>6</v>
@@ -4047,28 +4358,28 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="K33" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="O33" s="4"/>
     </row>
     <row r="34" spans="2:15">
       <c r="B34" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -4077,26 +4388,80 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="K34"/>
       <c r="M34" s="4" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="2:15">
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="B35" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35">
+        <v>0.46</v>
+      </c>
+      <c r="F35" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="36" spans="2:15">
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
+      <c r="B36" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36">
+        <v>0.49</v>
+      </c>
+      <c r="F36" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>199</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="37" spans="2:15">
       <c r="M37" s="4"/>
@@ -4149,10 +4514,10 @@
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -4169,126 +4534,126 @@
     </row>
     <row r="2" spans="1:14">
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" s="6" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="6" t="s">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>149</v>
+        <v>355</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="6" t="s">
-        <v>291</v>
+        <v>356</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>147</v>
+        <v>357</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="6" t="s">
-        <v>292</v>
+        <v>359</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4316,50 +4681,50 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="B3" s="6" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4367,19 +4732,19 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4387,19 +4752,19 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4407,19 +4772,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4427,19 +4792,19 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4447,19 +4812,19 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4467,19 +4832,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G9" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4487,19 +4852,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4507,19 +4872,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G11" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4527,19 +4892,19 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4547,19 +4912,19 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4567,19 +4932,19 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4587,19 +4952,19 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4607,19 +4972,19 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -4627,19 +4992,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
-        <v>320</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -4647,19 +5012,19 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -4667,19 +5032,19 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -4687,19 +5052,19 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -4707,19 +5072,19 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -4727,13 +5092,13 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -4741,13 +5106,13 @@
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -4755,19 +5120,19 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G24" t="s">
-        <v>327</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -4775,19 +5140,19 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>329</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -4795,19 +5160,19 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -4815,19 +5180,19 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -4835,19 +5200,19 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -4855,19 +5220,19 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G29" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -4875,19 +5240,19 @@
         <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -4895,19 +5260,19 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -4915,19 +5280,19 @@
         <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="2:7">
@@ -4935,13 +5300,13 @@
         <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -4949,16 +5314,16 @@
         <v>31</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -4966,16 +5331,16 @@
         <v>32</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -4983,16 +5348,16 @@
         <v>33</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="2:7">
@@ -5000,13 +5365,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="2:7">
@@ -5014,13 +5379,13 @@
         <v>35</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="2:7">
@@ -5028,19 +5393,19 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="F39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="2:7">
@@ -5048,19 +5413,19 @@
         <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D40">
         <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>344</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="2:7">
@@ -5068,19 +5433,19 @@
         <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="F41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="2:7">
@@ -5088,13 +5453,13 @@
         <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="G42" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="2:7">
@@ -5102,13 +5467,13 @@
         <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
       <c r="G43" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="2:7">
@@ -5116,19 +5481,19 @@
         <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="F44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G44" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="2:7">
@@ -5136,19 +5501,19 @@
         <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G45" t="s">
-        <v>347</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -5156,13 +5521,13 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D46">
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" spans="2:7">
@@ -5170,13 +5535,13 @@
         <v>44</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="G47" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" spans="2:7">
@@ -5184,13 +5549,13 @@
         <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D48">
         <v>5</v>
       </c>
       <c r="G48" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="2:2">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="368">
   <si>
     <t>!Enum</t>
   </si>
@@ -1196,93 +1196,35 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_GreatSword_Attack_02_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Attack_03_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ComboNext</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_02</t>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Attack_02_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_03</t>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Attack_03_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대검 기본공격 2타</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대검 기본공격 3타</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ComboClose</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ComboOpen</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>대검 기본공격 1타</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Attack1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Attack_01_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Attack_01_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>blade_hit_08</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboSteps</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2435,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="13" customWidth="1"/>
@@ -2455,14 +2397,12 @@
     <col min="20" max="20" width="13.75" style="6" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.25" style="6" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="30.625" style="6" customWidth="1"/>
-    <col min="24" max="24" width="12.625" style="6" customWidth="1"/>
-    <col min="25" max="25" width="14.625" style="6" customWidth="1"/>
-    <col min="26" max="30" width="9" style="6" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="6"/>
+    <col min="23" max="23" width="12.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="9" style="6" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="10" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:23" s="10" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>109</v>
       </c>
@@ -2470,7 +2410,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:23">
       <c r="B2" s="6" t="s">
         <v>110</v>
       </c>
@@ -2535,16 +2475,10 @@
         <v>130</v>
       </c>
       <c r="W2" t="s">
-        <v>362</v>
-      </c>
-      <c r="X2" t="s">
-        <v>376</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="B3" s="6" t="s">
         <v>131</v>
       </c>
@@ -2609,27 +2543,21 @@
         <v>134</v>
       </c>
       <c r="W3" t="s">
-        <v>363</v>
-      </c>
-      <c r="X3" t="s">
-        <v>374</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="B4" s="6" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
@@ -2653,22 +2581,16 @@
         <v>1</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="V4">
         <v>1</v>
       </c>
-      <c r="W4" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="W4" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="B5" s="6" t="s">
         <v>311</v>
       </c>
@@ -2712,7 +2634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:23">
       <c r="B6" s="6" t="s">
         <v>314</v>
       </c>
@@ -2747,7 +2669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:23">
       <c r="B7" s="6" t="s">
         <v>317</v>
       </c>
@@ -2761,7 +2683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:23">
       <c r="B8" s="6" t="s">
         <v>319</v>
       </c>
@@ -2802,7 +2724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:23">
       <c r="B9" s="6" t="s">
         <v>322</v>
       </c>
@@ -2816,7 +2738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:23">
       <c r="B10" s="6" t="s">
         <v>324</v>
       </c>
@@ -2827,7 +2749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:23">
       <c r="B11" s="6" t="s">
         <v>326</v>
       </c>
@@ -2868,7 +2790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:23">
       <c r="B12" s="6" t="s">
         <v>329</v>
       </c>
@@ -2882,7 +2804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:23">
       <c r="B13" s="6" t="s">
         <v>331</v>
       </c>
@@ -2893,7 +2815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:23">
       <c r="B14" s="6" t="s">
         <v>333</v>
       </c>
@@ -2934,7 +2856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:23">
       <c r="B15" s="6" t="s">
         <v>336</v>
       </c>
@@ -2948,7 +2870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:23">
       <c r="B16" s="6" t="s">
         <v>338</v>
       </c>
@@ -2959,7 +2881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:22">
       <c r="B17" s="6" t="s">
         <v>142</v>
       </c>
@@ -2994,7 +2916,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:22">
       <c r="B18" s="6" t="s">
         <v>145</v>
       </c>
@@ -3032,7 +2954,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:22">
       <c r="B19" s="6" t="s">
         <v>148</v>
       </c>
@@ -3073,7 +2995,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:22">
       <c r="B20" s="6" t="s">
         <v>151</v>
       </c>
@@ -3114,7 +3036,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:22">
       <c r="B21" t="s">
         <v>154</v>
       </c>
@@ -3152,7 +3074,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:22">
       <c r="B22" t="s">
         <v>157</v>
       </c>
@@ -3184,7 +3106,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:22">
       <c r="B23" s="4" t="s">
         <v>340</v>
       </c>
@@ -3204,7 +3126,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:22">
       <c r="B24" s="4" t="s">
         <v>160</v>
       </c>
@@ -3239,7 +3161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:22">
       <c r="B25" s="4" t="s">
         <v>165</v>
       </c>
@@ -3274,7 +3196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:22">
       <c r="B26" s="4" t="s">
         <v>170</v>
       </c>
@@ -3309,7 +3231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:22">
       <c r="B27" t="s">
         <v>175</v>
       </c>
@@ -3335,7 +3257,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:22">
       <c r="B28" t="s">
         <v>180</v>
       </c>
@@ -3370,7 +3292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:22">
       <c r="B29" s="6" t="s">
         <v>302</v>
       </c>
@@ -3403,103 +3325,6 @@
       </c>
       <c r="P29" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25">
-      <c r="B30" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="H30" s="6">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M30" s="6">
-        <v>2</v>
-      </c>
-      <c r="N30" s="6">
-        <v>240</v>
-      </c>
-      <c r="O30" s="6">
-        <v>1</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="V30">
-        <v>1</v>
-      </c>
-      <c r="W30" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="X30" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Y30" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25">
-      <c r="B31" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="H31" s="6">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M31" s="6">
-        <v>2</v>
-      </c>
-      <c r="N31" s="6">
-        <v>240</v>
-      </c>
-      <c r="O31" s="6">
-        <v>1</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="X31" s="6">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Y31" s="6">
-        <v>1.08</v>
       </c>
     </row>
   </sheetData>
@@ -3511,7 +3336,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3635,7 +3460,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="6" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
@@ -3662,7 +3487,7 @@
         <v>200</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -4400,68 +4225,14 @@
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="2:15">
-      <c r="B35" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35">
-        <v>0.46</v>
-      </c>
-      <c r="F35" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="H35" s="6">
-        <v>1</v>
-      </c>
-      <c r="J35" t="s">
-        <v>199</v>
-      </c>
-      <c r="L35" t="b">
-        <v>1</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N35" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
     </row>
     <row r="36" spans="2:15">
-      <c r="B36" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36">
-        <v>0.49</v>
-      </c>
-      <c r="F36" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="H36" s="6">
-        <v>1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>199</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
     </row>
     <row r="37" spans="2:15">
       <c r="M37" s="4"/>
@@ -4472,16 +4243,6 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-    </row>
-    <row r="39" spans="2:15">
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-    </row>
-    <row r="40" spans="2:15">
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -1036,10 +1036,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>도 기본공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_Blade_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1048,46 +1044,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>도 강타스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Blade_Passive_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>도 패시브 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Pistol_Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총 기본공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_Pistol_Attack_Projectile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Pistol_Active_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총 강타스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Pistol_Passive_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총 패시브 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Rifle_Attack</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1132,18 +1092,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_Pistol_Attack_Projectile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PJT_Pistol_Bullet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_Pistol_Attack_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_Rifle_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1225,6 +1173,58 @@
   </si>
   <si>
     <t>SE_GreatSword_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Shuriken_Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검 기본공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Shuriken_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Shuriken_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Shuriken_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도 기본공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Shuriken_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJT_Shuriken_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Shuriken_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1776,7 +1776,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2475,7 +2475,7 @@
         <v>130</v>
       </c>
       <c r="W2" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -2543,21 +2543,21 @@
         <v>134</v>
       </c>
       <c r="W3" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="6" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="V4">
         <v>1</v>
@@ -2688,7 +2688,7 @@
         <v>319</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
@@ -2718,7 +2718,7 @@
         <v>0.5</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V8">
         <v>1</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>4</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="6" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
@@ -2784,7 +2784,7 @@
         <v>0.5</v>
       </c>
       <c r="P11" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="V11">
         <v>1</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="6" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>4</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="6" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>6</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
@@ -2850,7 +2850,7 @@
         <v>0.5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="V14">
         <v>1</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="6" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>4</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="6" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="23" spans="2:22">
       <c r="B23" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C23" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -3123,7 +3123,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="2:22">
@@ -3460,7 +3460,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="6" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
@@ -3487,12 +3487,12 @@
         <v>200</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C5" t="s">
         <v>54</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>62</v>
@@ -3536,7 +3536,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C7" t="s">
         <v>54</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
         <v>54</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C18" t="s">
         <v>54</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="25" spans="2:15">
       <c r="B25" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C25" t="s">
         <v>64</v>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="26" spans="2:15">
       <c r="B26" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C26" t="s">
         <v>60</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="27" spans="2:15">
       <c r="B27" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
@@ -4025,7 +4025,7 @@
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -4365,13 +4365,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>92</v>
@@ -4382,13 +4382,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="6" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>98</v>
@@ -4397,18 +4397,18 @@
         <v>89</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="6" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>92</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -2697,7 +2697,7 @@
         <v>140</v>
       </c>
       <c r="H8" s="6">
-        <v>0.41670000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>9</v>
@@ -2709,10 +2709,10 @@
         <v>44</v>
       </c>
       <c r="M8" s="6">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N8" s="6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O8" s="6">
         <v>0.5</v>
@@ -3501,7 +3501,7 @@
         <v>50</v>
       </c>
       <c r="E5" s="6">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="6">
         <v>1.2</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -1776,7 +1776,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2709,7 +2709,7 @@
         <v>44</v>
       </c>
       <c r="M8" s="6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N8" s="6">
         <v>90</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="370">
   <si>
     <t>!Enum</t>
   </si>
@@ -1056,31 +1056,47 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Skill_Rifle_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총 강타스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rifle_Passive_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총 패시브 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Passive_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 스파크 소환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Passive_02_Summon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Blade_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>SE_Rifle_Attack_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Rifle_Active_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>소총 강타스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Rifle_Passive_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>소총 패시브 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Passive_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대검 스파크 소환</t>
+    <t>SE_GreatSword_Active_01_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_02_Damage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1088,11 +1104,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_Blade_Attack_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_Rifle_Attack_Damage</t>
+    <t>SE_GreatSword_AtkSpeedUp_StatChange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_Active_01_AtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_GreatSword_AtkSpeedUp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_Active_01_Ratio</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1100,15 +1124,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_GreatSword_Active_02_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Passive_02_Summon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_AtkSpeedUp_StatChange</t>
+    <t>SKM_GreatSword_Active_01_AppendAtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Active_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1116,30 +1136,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BUFF_GreatSword_AtkSpeedUp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKM_GreatSword_Active_01_Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Active_01_Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKM_GreatSword_Active_01_AppendAtkSpeedBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Active_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_GreatSword_Active_01_AtkSpeedBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SKM_GreatSword_AtkSpeedBuff_Ratio</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1225,6 +1221,18 @@
   </si>
   <si>
     <t>SE_Shuriken_Attack_Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Rifle_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_Rifle_Attack_Projectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PJT_Rifle_Bullet</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2475,7 +2483,7 @@
         <v>130</v>
       </c>
       <c r="W2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -2543,21 +2551,21 @@
         <v>134</v>
       </c>
       <c r="W3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="B4" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
@@ -2581,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="V4">
         <v>1</v>
@@ -2688,7 +2696,7 @@
         <v>319</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
@@ -2729,7 +2737,7 @@
         <v>321</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>4</v>
@@ -2743,7 +2751,7 @@
         <v>322</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>6</v>
@@ -2751,10 +2759,10 @@
     </row>
     <row r="11" spans="1:23">
       <c r="B11" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>355</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>356</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
@@ -2784,7 +2792,7 @@
         <v>0.5</v>
       </c>
       <c r="P11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="V11">
         <v>1</v>
@@ -2792,10 +2800,10 @@
     </row>
     <row r="12" spans="1:23">
       <c r="B12" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>359</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>4</v>
@@ -2806,10 +2814,10 @@
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>360</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>361</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>6</v>
@@ -2829,7 +2837,7 @@
         <v>140</v>
       </c>
       <c r="H14" s="6">
-        <v>0.83333330000000005</v>
+        <v>0.5</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>9</v>
@@ -2841,16 +2849,16 @@
         <v>50</v>
       </c>
       <c r="M14" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="6">
         <v>0.5</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="V14">
         <v>1</v>
@@ -2858,10 +2866,10 @@
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>4</v>
@@ -2872,10 +2880,10 @@
     </row>
     <row r="16" spans="1:23">
       <c r="B16" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
@@ -3108,10 +3116,10 @@
     </row>
     <row r="23" spans="2:22">
       <c r="B23" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23" t="s">
         <v>330</v>
-      </c>
-      <c r="C23" t="s">
-        <v>331</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -3123,7 +3131,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="2:22">
@@ -3460,7 +3468,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
@@ -3487,12 +3495,12 @@
         <v>200</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
         <v>54</v>
@@ -3524,7 +3532,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>62</v>
@@ -3536,7 +3544,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3547,7 +3555,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C7" t="s">
         <v>54</v>
@@ -3576,7 +3584,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="B8" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C8" t="s">
         <v>54</v>
@@ -3585,10 +3593,10 @@
         <v>50</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -3798,7 +3806,7 @@
     </row>
     <row r="18" spans="2:15">
       <c r="B18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C18" t="s">
         <v>54</v>
@@ -3828,7 +3836,7 @@
     </row>
     <row r="19" spans="2:15">
       <c r="B19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
@@ -3971,7 +3979,7 @@
     </row>
     <row r="25" spans="2:15">
       <c r="B25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C25" t="s">
         <v>64</v>
@@ -3998,7 +4006,7 @@
     </row>
     <row r="26" spans="2:15">
       <c r="B26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C26" t="s">
         <v>60</v>
@@ -4016,7 +4024,7 @@
     </row>
     <row r="27" spans="2:15">
       <c r="B27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
@@ -4025,7 +4033,7 @@
         <v>73</v>
       </c>
       <c r="F27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -4225,9 +4233,27 @@
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="2:15">
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="B35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>369</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="2:15">
       <c r="M36" s="4"/>
@@ -4365,13 +4391,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>92</v>
@@ -4382,13 +4408,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>98</v>
@@ -4397,18 +4423,18 @@
         <v>89</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>92</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -2717,10 +2717,10 @@
         <v>44</v>
       </c>
       <c r="M8" s="6">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N8" s="6">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="O8" s="6">
         <v>0.5</v>
@@ -2771,7 +2771,7 @@
         <v>140</v>
       </c>
       <c r="H11" s="6">
-        <v>0.83333330000000005</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>9</v>
@@ -2796,6 +2796,9 @@
       </c>
       <c r="V11">
         <v>1</v>
+      </c>
+      <c r="W11" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -3541,7 +3544,7 @@
         <v>73</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.4166667</v>
       </c>
       <c r="F6" t="s">
         <v>365</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="371">
   <si>
     <t>!Enum</t>
   </si>
@@ -1233,6 +1233,10 @@
   </si>
   <si>
     <t>PJT_Rifle_Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1784,7 +1788,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2714,13 +2718,13 @@
         <v>34</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>44</v>
+        <v>370</v>
       </c>
       <c r="M8" s="6">
         <v>2.5</v>
       </c>
       <c r="N8" s="6">
-        <v>60</v>
+        <v>0.75</v>
       </c>
       <c r="O8" s="6">
         <v>0.5</v>
